--- a/research/traditional_assets/database/data/morocco/morocco_chemical_basic.xlsx
+++ b/research/traditional_assets/database/data/morocco/morocco_chemical_basic.xlsx
@@ -1404,7 +1404,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1541,22 +1541,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1152685924699146</v>
+        <v>0.1149303329740109</v>
       </c>
       <c r="C2">
-        <v>90.17163400807925</v>
+        <v>89.70497687171596</v>
       </c>
       <c r="D2">
-        <v>89.35963400807925</v>
+        <v>89.79687687171595</v>
       </c>
       <c r="E2">
-        <v>-1.29</v>
+        <v>-0.3861</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.9039</v>
       </c>
       <c r="G2">
         <v>0.8120000000000001</v>
@@ -1577,28 +1577,28 @@
         <v>6.58</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.04546617</v>
       </c>
       <c r="N2">
-        <v>6.58</v>
+        <v>6.53453383</v>
       </c>
       <c r="O2">
-        <v>2.1056</v>
+        <v>2.0910508256</v>
       </c>
       <c r="P2">
-        <v>4.4744</v>
+        <v>4.4434830044</v>
       </c>
       <c r="Q2">
-        <v>-2.1056</v>
+        <v>-2.1365169956</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1152685924699146</v>
+        <v>0.1157457504787989</v>
       </c>
       <c r="T2">
-        <v>0.9054086395470866</v>
+        <v>0.9116276079803394</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>144.72298854291</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1623,22 +1623,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1149303329740109</v>
+        <v>0.1145920734781072</v>
       </c>
       <c r="C3">
-        <v>89.70497687171596</v>
+        <v>89.24261969443698</v>
       </c>
       <c r="D3">
-        <v>89.79687687171595</v>
+        <v>90.23841969443698</v>
       </c>
       <c r="E3">
-        <v>-0.3861</v>
+        <v>0.5178</v>
       </c>
       <c r="F3">
-        <v>0.9039</v>
+        <v>1.8078</v>
       </c>
       <c r="G3">
         <v>0.8120000000000001</v>
@@ -1659,28 +1659,28 @@
         <v>6.58</v>
       </c>
       <c r="M3">
-        <v>0.04546617</v>
+        <v>0.09093234</v>
       </c>
       <c r="N3">
-        <v>6.53453383</v>
+        <v>6.48906766</v>
       </c>
       <c r="O3">
-        <v>2.0910508256</v>
+        <v>2.0765016512</v>
       </c>
       <c r="P3">
-        <v>4.4434830044</v>
+        <v>4.4125660088</v>
       </c>
       <c r="Q3">
-        <v>-2.1365169956</v>
+        <v>-2.1674339912</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1157457504787989</v>
+        <v>0.1162326464062318</v>
       </c>
       <c r="T3">
-        <v>0.9116276079803394</v>
+        <v>0.9179734941367196</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1697,7 +1697,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>144.72298854291</v>
+        <v>72.36149427145502</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1705,22 +1705,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1145920734781072</v>
+        <v>0.1142538139822034</v>
       </c>
       <c r="C4">
-        <v>89.24261969443698</v>
+        <v>88.78462622003867</v>
       </c>
       <c r="D4">
-        <v>90.23841969443698</v>
+        <v>90.68432622003867</v>
       </c>
       <c r="E4">
-        <v>0.5178</v>
+        <v>1.4217</v>
       </c>
       <c r="F4">
-        <v>1.8078</v>
+        <v>2.7117</v>
       </c>
       <c r="G4">
         <v>0.8120000000000001</v>
@@ -1741,28 +1741,28 @@
         <v>6.58</v>
       </c>
       <c r="M4">
-        <v>0.09093234</v>
+        <v>0.13639851</v>
       </c>
       <c r="N4">
-        <v>6.48906766</v>
+        <v>6.44360149</v>
       </c>
       <c r="O4">
-        <v>2.0765016512</v>
+        <v>2.0619524768</v>
       </c>
       <c r="P4">
-        <v>4.4125660088</v>
+        <v>4.3816490132</v>
       </c>
       <c r="Q4">
-        <v>-2.1674339912</v>
+        <v>-2.1983509868</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1162326464062318</v>
+        <v>0.116729581424952</v>
       </c>
       <c r="T4">
-        <v>0.9179734941367196</v>
+        <v>0.9244502233066336</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>72.36149427145502</v>
+        <v>48.24099618097001</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1787,22 +1787,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1142538139822034</v>
+        <v>0.1139155544862997</v>
       </c>
       <c r="C5">
-        <v>88.78462622003867</v>
+        <v>88.33106145851538</v>
       </c>
       <c r="D5">
-        <v>90.68432622003867</v>
+        <v>91.13466145851538</v>
       </c>
       <c r="E5">
-        <v>1.4217</v>
+        <v>2.3256</v>
       </c>
       <c r="F5">
-        <v>2.7117</v>
+        <v>3.6156</v>
       </c>
       <c r="G5">
         <v>0.8120000000000001</v>
@@ -1823,28 +1823,28 @@
         <v>6.58</v>
       </c>
       <c r="M5">
-        <v>0.13639851</v>
+        <v>0.18186468</v>
       </c>
       <c r="N5">
-        <v>6.44360149</v>
+        <v>6.39813532</v>
       </c>
       <c r="O5">
-        <v>2.0619524768</v>
+        <v>2.0474033024</v>
       </c>
       <c r="P5">
-        <v>4.3816490132</v>
+        <v>4.3507320176</v>
       </c>
       <c r="Q5">
-        <v>-2.1983509868</v>
+        <v>-2.2292679824</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.116729581424952</v>
+        <v>0.1172368692565622</v>
       </c>
       <c r="T5">
-        <v>0.9244502233066336</v>
+        <v>0.9310618843342541</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>48.24099618097001</v>
+        <v>36.18074713572751</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1869,22 +1869,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1139155544862997</v>
+        <v>0.113577294990396</v>
       </c>
       <c r="C6">
-        <v>88.33106145851538</v>
+        <v>87.88199171765574</v>
       </c>
       <c r="D6">
-        <v>91.13466145851538</v>
+        <v>91.58949171765573</v>
       </c>
       <c r="E6">
-        <v>2.3256</v>
+        <v>3.2295</v>
       </c>
       <c r="F6">
-        <v>3.6156</v>
+        <v>4.5195</v>
       </c>
       <c r="G6">
         <v>0.8120000000000001</v>
@@ -1905,28 +1905,28 @@
         <v>6.58</v>
       </c>
       <c r="M6">
-        <v>0.18186468</v>
+        <v>0.22733085</v>
       </c>
       <c r="N6">
-        <v>6.39813532</v>
+        <v>6.352669150000001</v>
       </c>
       <c r="O6">
-        <v>2.0474033024</v>
+        <v>2.032854128</v>
       </c>
       <c r="P6">
-        <v>4.3507320176</v>
+        <v>4.319815022</v>
       </c>
       <c r="Q6">
-        <v>-2.2292679824</v>
+        <v>-2.260184978</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1172368692565622</v>
+        <v>0.1177548368319958</v>
       </c>
       <c r="T6">
-        <v>0.9310618843342541</v>
+        <v>0.937812738225614</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1943,7 +1943,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>36.18074713572751</v>
+        <v>28.94459770858201</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.113577294990396</v>
+        <v>0.1132390354944922</v>
       </c>
       <c r="C7">
-        <v>87.88199171765574</v>
+        <v>87.43748463559007</v>
       </c>
       <c r="D7">
-        <v>91.58949171765573</v>
+        <v>92.04888463559007</v>
       </c>
       <c r="E7">
-        <v>3.2295</v>
+        <v>4.133400000000001</v>
       </c>
       <c r="F7">
-        <v>4.5195</v>
+        <v>5.423400000000001</v>
       </c>
       <c r="G7">
         <v>0.8120000000000001</v>
@@ -1987,28 +1987,28 @@
         <v>6.58</v>
       </c>
       <c r="M7">
-        <v>0.22733085</v>
+        <v>0.2727970200000001</v>
       </c>
       <c r="N7">
-        <v>6.352669150000001</v>
+        <v>6.30720298</v>
       </c>
       <c r="O7">
-        <v>2.032854128</v>
+        <v>2.0183049536</v>
       </c>
       <c r="P7">
-        <v>4.319815022</v>
+        <v>4.2888980264</v>
       </c>
       <c r="Q7">
-        <v>-2.260184978</v>
+        <v>-2.2911019736</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1177548368319958</v>
+        <v>0.1182838249941407</v>
       </c>
       <c r="T7">
-        <v>0.937812738225614</v>
+        <v>0.9447072273061516</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2025,7 +2025,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>28.94459770858201</v>
+        <v>24.120498090485</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2033,22 +2033,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1132390354944922</v>
+        <v>0.1129007759985885</v>
       </c>
       <c r="C8">
-        <v>87.43748463559007</v>
+        <v>86.99760921432207</v>
       </c>
       <c r="D8">
-        <v>92.04888463559007</v>
+        <v>92.51290921432206</v>
       </c>
       <c r="E8">
-        <v>4.1334</v>
+        <v>5.037299999999999</v>
       </c>
       <c r="F8">
-        <v>5.4234</v>
+        <v>6.327299999999999</v>
       </c>
       <c r="G8">
         <v>0.8120000000000001</v>
@@ -2069,28 +2069,28 @@
         <v>6.58</v>
       </c>
       <c r="M8">
-        <v>0.27279702</v>
+        <v>0.31826319</v>
       </c>
       <c r="N8">
-        <v>6.30720298</v>
+        <v>6.26173681</v>
       </c>
       <c r="O8">
-        <v>2.0183049536</v>
+        <v>2.0037557792</v>
       </c>
       <c r="P8">
-        <v>4.2888980264</v>
+        <v>4.2579810308</v>
       </c>
       <c r="Q8">
-        <v>-2.2911019736</v>
+        <v>-2.3220189692</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1182838249941407</v>
+        <v>0.1188241892457941</v>
       </c>
       <c r="T8">
-        <v>0.9447072273061516</v>
+        <v>0.9517499849690666</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2107,7 +2107,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>24.12049809048501</v>
+        <v>20.67471264898715</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2115,22 +2115,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1129007759985885</v>
+        <v>0.1125625165026848</v>
       </c>
       <c r="C9">
-        <v>86.99760921432207</v>
+        <v>86.56243585427977</v>
       </c>
       <c r="D9">
-        <v>92.51290921432206</v>
+        <v>92.98163585427977</v>
       </c>
       <c r="E9">
-        <v>5.037300000000001</v>
+        <v>5.9412</v>
       </c>
       <c r="F9">
-        <v>6.327300000000001</v>
+        <v>7.2312</v>
       </c>
       <c r="G9">
         <v>0.8120000000000001</v>
@@ -2151,28 +2151,28 @@
         <v>6.58</v>
       </c>
       <c r="M9">
-        <v>0.31826319</v>
+        <v>0.36372936</v>
       </c>
       <c r="N9">
-        <v>6.26173681</v>
+        <v>6.21627064</v>
       </c>
       <c r="O9">
-        <v>2.0037557792</v>
+        <v>1.9892066048</v>
       </c>
       <c r="P9">
-        <v>4.2579810308</v>
+        <v>4.2270640352</v>
       </c>
       <c r="Q9">
-        <v>-2.3220189692</v>
+        <v>-2.3529359648</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1188241892457941</v>
+        <v>0.1193763005463965</v>
       </c>
       <c r="T9">
-        <v>0.9517499849690666</v>
+        <v>0.9589458460594361</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>20.67471264898715</v>
+        <v>18.09037356786375</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2197,22 +2197,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1125625165026848</v>
+        <v>0.1122242570067811</v>
       </c>
       <c r="C10">
-        <v>86.56243585427977</v>
+        <v>86.13203638992236</v>
       </c>
       <c r="D10">
-        <v>92.98163585427977</v>
+        <v>93.45513638992236</v>
       </c>
       <c r="E10">
-        <v>5.9412</v>
+        <v>6.8451</v>
       </c>
       <c r="F10">
-        <v>7.2312</v>
+        <v>8.1351</v>
       </c>
       <c r="G10">
         <v>0.8120000000000001</v>
@@ -2233,28 +2233,28 @@
         <v>6.58</v>
       </c>
       <c r="M10">
-        <v>0.36372936</v>
+        <v>0.40919553</v>
       </c>
       <c r="N10">
-        <v>6.21627064</v>
+        <v>6.17080447</v>
       </c>
       <c r="O10">
-        <v>1.9892066048</v>
+        <v>1.9746574304</v>
       </c>
       <c r="P10">
-        <v>4.2270640352</v>
+        <v>4.1961470396</v>
       </c>
       <c r="Q10">
-        <v>-2.3529359648</v>
+        <v>-2.3838529604</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1193763005463965</v>
+        <v>0.1199405461612979</v>
       </c>
       <c r="T10">
-        <v>0.9589458460594361</v>
+        <v>0.9662998579430007</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>18.09037356786375</v>
+        <v>16.08033206032334</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2279,22 +2279,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1122242570067811</v>
+        <v>0.1118859975108774</v>
       </c>
       <c r="C11">
-        <v>86.13203638992236</v>
+        <v>85.70648412644044</v>
       </c>
       <c r="D11">
-        <v>93.45513638992236</v>
+        <v>93.93348412644045</v>
       </c>
       <c r="E11">
-        <v>6.8451</v>
+        <v>7.749</v>
       </c>
       <c r="F11">
-        <v>8.1351</v>
+        <v>9.039</v>
       </c>
       <c r="G11">
         <v>0.8120000000000001</v>
@@ -2315,28 +2315,28 @@
         <v>6.58</v>
       </c>
       <c r="M11">
-        <v>0.40919553</v>
+        <v>0.4546616999999999</v>
       </c>
       <c r="N11">
-        <v>6.17080447</v>
+        <v>6.1253383</v>
       </c>
       <c r="O11">
-        <v>1.9746574304</v>
+        <v>1.960108256</v>
       </c>
       <c r="P11">
-        <v>4.1961470396</v>
+        <v>4.165230044</v>
       </c>
       <c r="Q11">
-        <v>-2.3838529604</v>
+        <v>-2.414769956</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1199405461612979</v>
+        <v>0.1205173305676415</v>
       </c>
       <c r="T11">
-        <v>0.9662998579430007</v>
+        <v>0.9738172923128665</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2353,7 +2353,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>16.08033206032334</v>
+        <v>14.47229885429101</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2361,22 +2361,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1118859975108774</v>
+        <v>0.1115477380149736</v>
       </c>
       <c r="C12">
-        <v>85.70648412644044</v>
+        <v>85.28585387758923</v>
       </c>
       <c r="D12">
-        <v>93.93348412644045</v>
+        <v>94.41675387758923</v>
       </c>
       <c r="E12">
-        <v>7.749</v>
+        <v>8.652899999999999</v>
       </c>
       <c r="F12">
-        <v>9.039</v>
+        <v>9.9429</v>
       </c>
       <c r="G12">
         <v>0.8120000000000001</v>
@@ -2397,28 +2397,28 @@
         <v>6.58</v>
       </c>
       <c r="M12">
-        <v>0.4546616999999999</v>
+        <v>0.5001278699999999</v>
       </c>
       <c r="N12">
-        <v>6.1253383</v>
+        <v>6.07987213</v>
       </c>
       <c r="O12">
-        <v>1.960108256</v>
+        <v>1.9455590816</v>
       </c>
       <c r="P12">
-        <v>4.165230044</v>
+        <v>4.1343130484</v>
       </c>
       <c r="Q12">
-        <v>-2.414769956</v>
+        <v>-2.4456869516</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1205173305676415</v>
+        <v>0.1211070764213187</v>
       </c>
       <c r="T12">
-        <v>0.9738172923128665</v>
+        <v>0.9815036577921675</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2435,7 +2435,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>14.47229885429101</v>
+        <v>13.15663532208273</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2443,22 +2443,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1115477380149736</v>
+        <v>0.1113318785190699</v>
       </c>
       <c r="C13">
-        <v>85.28585387758923</v>
+        <v>84.69295904572202</v>
       </c>
       <c r="D13">
-        <v>94.41675387758923</v>
+        <v>94.72775904572202</v>
       </c>
       <c r="E13">
-        <v>8.652899999999999</v>
+        <v>9.556799999999999</v>
       </c>
       <c r="F13">
-        <v>9.9429</v>
+        <v>10.8468</v>
       </c>
       <c r="G13">
         <v>0.8120000000000001</v>
@@ -2479,45 +2479,45 @@
         <v>6.58</v>
       </c>
       <c r="M13">
-        <v>0.5001278699999999</v>
+        <v>0.56186424</v>
       </c>
       <c r="N13">
-        <v>6.07987213</v>
+        <v>6.01813576</v>
       </c>
       <c r="O13">
-        <v>1.9455590816</v>
+        <v>1.9258034432</v>
       </c>
       <c r="P13">
-        <v>4.1343130484</v>
+        <v>4.0923323168</v>
       </c>
       <c r="Q13">
-        <v>-2.4456869516</v>
+        <v>-2.4876676832</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1211070764213187</v>
+        <v>0.1217102255898521</v>
       </c>
       <c r="T13">
-        <v>0.9815036577921675</v>
+        <v>0.9893647133959983</v>
       </c>
       <c r="U13">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V13">
         <v>0.32</v>
       </c>
       <c r="W13">
-        <v>0.034204</v>
+        <v>0.035224</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>13.15663532208273</v>
+        <v>11.71101403427988</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2525,22 +2525,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1113318785190699</v>
+        <v>0.1110038190231662</v>
       </c>
       <c r="C14">
-        <v>84.69295904572202</v>
+        <v>84.26566212428695</v>
       </c>
       <c r="D14">
-        <v>94.72775904572202</v>
+        <v>95.20436212428694</v>
       </c>
       <c r="E14">
-        <v>9.556799999999999</v>
+        <v>10.4607</v>
       </c>
       <c r="F14">
-        <v>10.8468</v>
+        <v>11.7507</v>
       </c>
       <c r="G14">
         <v>0.8120000000000001</v>
@@ -2561,28 +2561,28 @@
         <v>6.58</v>
       </c>
       <c r="M14">
-        <v>0.56186424</v>
+        <v>0.60868626</v>
       </c>
       <c r="N14">
-        <v>6.01813576</v>
+        <v>5.97131374</v>
       </c>
       <c r="O14">
-        <v>1.9258034432</v>
+        <v>1.9108203968</v>
       </c>
       <c r="P14">
-        <v>4.0923323168</v>
+        <v>4.0604933432</v>
       </c>
       <c r="Q14">
-        <v>-2.4876676832</v>
+        <v>-2.5195066568</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1217102255898521</v>
+        <v>0.1223272402565128</v>
       </c>
       <c r="T14">
-        <v>0.9893647133959983</v>
+        <v>0.9974064829217562</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2599,7 +2599,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.71101403427988</v>
+        <v>10.81016680087374</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2607,22 +2607,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1110038190231662</v>
+        <v>0.1106757595272624</v>
       </c>
       <c r="C15">
-        <v>84.26566212428695</v>
+        <v>83.84318531337816</v>
       </c>
       <c r="D15">
-        <v>95.20436212428694</v>
+        <v>95.68578531337816</v>
       </c>
       <c r="E15">
-        <v>10.4607</v>
+        <v>11.3646</v>
       </c>
       <c r="F15">
-        <v>11.7507</v>
+        <v>12.6546</v>
       </c>
       <c r="G15">
         <v>0.8120000000000001</v>
@@ -2643,28 +2643,28 @@
         <v>6.58</v>
       </c>
       <c r="M15">
-        <v>0.60868626</v>
+        <v>0.6555082800000001</v>
       </c>
       <c r="N15">
-        <v>5.97131374</v>
+        <v>5.92449172</v>
       </c>
       <c r="O15">
-        <v>1.9108203968</v>
+        <v>1.8958373504</v>
       </c>
       <c r="P15">
-        <v>4.0604933432</v>
+        <v>4.0286543696</v>
       </c>
       <c r="Q15">
-        <v>-2.5195066568</v>
+        <v>-2.5513456304</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1223272402565128</v>
+        <v>0.1229586041014679</v>
       </c>
       <c r="T15">
-        <v>0.9974064829217562</v>
+        <v>1.005635270343462</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2681,7 +2681,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>10.81016680087374</v>
+        <v>10.03801202938276</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2689,22 +2689,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1106757595272624</v>
+        <v>0.1105211000313587</v>
       </c>
       <c r="C16">
-        <v>83.84318531337816</v>
+        <v>83.16793895669613</v>
       </c>
       <c r="D16">
-        <v>95.68578531337816</v>
+        <v>95.91443895669613</v>
       </c>
       <c r="E16">
-        <v>11.3646</v>
+        <v>12.2685</v>
       </c>
       <c r="F16">
-        <v>12.6546</v>
+        <v>13.5585</v>
       </c>
       <c r="G16">
         <v>0.8120000000000001</v>
@@ -2725,45 +2725,45 @@
         <v>6.58</v>
       </c>
       <c r="M16">
-        <v>0.6555082800000001</v>
+        <v>0.7253797500000001</v>
       </c>
       <c r="N16">
-        <v>5.92449172</v>
+        <v>5.85462025</v>
       </c>
       <c r="O16">
-        <v>1.8958373504</v>
+        <v>1.87347848</v>
       </c>
       <c r="P16">
-        <v>4.0286543696</v>
+        <v>3.98114177</v>
       </c>
       <c r="Q16">
-        <v>-2.5513456304</v>
+        <v>-2.59885823</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1229586041014679</v>
+        <v>0.1236048235663044</v>
       </c>
       <c r="T16">
-        <v>1.005635270343462</v>
+        <v>1.014057676292737</v>
       </c>
       <c r="U16">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V16">
         <v>0.32</v>
       </c>
       <c r="W16">
-        <v>0.035224</v>
+        <v>0.03638</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>10.03801202938276</v>
+        <v>9.071110683748753</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2771,22 +2771,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1105211000313587</v>
+        <v>0.110204600535455</v>
       </c>
       <c r="C17">
-        <v>83.16793895669613</v>
+        <v>82.73538527865604</v>
       </c>
       <c r="D17">
-        <v>95.91443895669613</v>
+        <v>96.38578527865604</v>
       </c>
       <c r="E17">
-        <v>12.2685</v>
+        <v>13.1724</v>
       </c>
       <c r="F17">
-        <v>13.5585</v>
+        <v>14.4624</v>
       </c>
       <c r="G17">
         <v>0.8120000000000001</v>
@@ -2807,28 +2807,28 @@
         <v>6.58</v>
       </c>
       <c r="M17">
-        <v>0.72537975</v>
+        <v>0.7737384</v>
       </c>
       <c r="N17">
-        <v>5.85462025</v>
+        <v>5.8062616</v>
       </c>
       <c r="O17">
-        <v>1.87347848</v>
+        <v>1.858003712</v>
       </c>
       <c r="P17">
-        <v>3.98114177</v>
+        <v>3.948257888</v>
       </c>
       <c r="Q17">
-        <v>-2.59885823</v>
+        <v>-2.631742112</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1236048235663044</v>
+        <v>0.124266429208875</v>
       </c>
       <c r="T17">
-        <v>1.014057676292737</v>
+        <v>1.022680615716995</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2845,7 +2845,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.071110683748755</v>
+        <v>8.504166266014456</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2853,22 +2853,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.110204600535455</v>
+        <v>0.1098881010395513</v>
       </c>
       <c r="C18">
-        <v>82.73538527865604</v>
+        <v>82.30748709425289</v>
       </c>
       <c r="D18">
-        <v>96.38578527865604</v>
+        <v>96.86178709425289</v>
       </c>
       <c r="E18">
-        <v>13.1724</v>
+        <v>14.0763</v>
       </c>
       <c r="F18">
-        <v>14.4624</v>
+        <v>15.3663</v>
       </c>
       <c r="G18">
         <v>0.8120000000000001</v>
@@ -2889,28 +2889,28 @@
         <v>6.58</v>
       </c>
       <c r="M18">
-        <v>0.7737384</v>
+        <v>0.82209705</v>
       </c>
       <c r="N18">
-        <v>5.8062616</v>
+        <v>5.75790295</v>
       </c>
       <c r="O18">
-        <v>1.858003712</v>
+        <v>1.842528944</v>
       </c>
       <c r="P18">
-        <v>3.948257888</v>
+        <v>3.915374006</v>
       </c>
       <c r="Q18">
-        <v>-2.631742112</v>
+        <v>-2.664625994</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.124266429208875</v>
+        <v>0.1249439771560859</v>
       </c>
       <c r="T18">
-        <v>1.022680615716995</v>
+        <v>1.031511336814127</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.504166266014456</v>
+        <v>8.003921191543018</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2935,22 +2935,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1098881010395513</v>
+        <v>0.1096695215436475</v>
       </c>
       <c r="C19">
-        <v>82.30748709425289</v>
+        <v>81.73507541737942</v>
       </c>
       <c r="D19">
-        <v>96.86178709425289</v>
+        <v>97.19327541737943</v>
       </c>
       <c r="E19">
-        <v>14.0763</v>
+        <v>14.9802</v>
       </c>
       <c r="F19">
-        <v>15.3663</v>
+        <v>16.2702</v>
       </c>
       <c r="G19">
         <v>0.8120000000000001</v>
@@ -2971,45 +2971,45 @@
         <v>6.58</v>
       </c>
       <c r="M19">
-        <v>0.82209705</v>
+        <v>0.8834718600000001</v>
       </c>
       <c r="N19">
-        <v>5.75790295</v>
+        <v>5.69652814</v>
       </c>
       <c r="O19">
-        <v>1.842528944</v>
+        <v>1.8228890048</v>
       </c>
       <c r="P19">
-        <v>3.915374006</v>
+        <v>3.8736391352</v>
       </c>
       <c r="Q19">
-        <v>-2.664625994</v>
+        <v>-2.7063608648</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1249439771560859</v>
+        <v>0.1256380506629848</v>
       </c>
       <c r="T19">
-        <v>1.031511336814127</v>
+        <v>1.040557441352652</v>
       </c>
       <c r="U19">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V19">
         <v>0.32</v>
       </c>
       <c r="W19">
-        <v>0.03638</v>
+        <v>0.036924</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y19">
-        <v>8.003921191543018</v>
+        <v>7.44788860620869</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1096695215436475</v>
+        <v>0.1093584620477438</v>
       </c>
       <c r="C20">
-        <v>81.73507541737941</v>
+        <v>81.30684600918589</v>
       </c>
       <c r="D20">
-        <v>97.19327541737941</v>
+        <v>97.66894600918589</v>
       </c>
       <c r="E20">
-        <v>14.9802</v>
+        <v>15.8841</v>
       </c>
       <c r="F20">
-        <v>16.2702</v>
+        <v>17.1741</v>
       </c>
       <c r="G20">
         <v>0.8120000000000001</v>
@@ -3053,28 +3053,28 @@
         <v>6.58</v>
       </c>
       <c r="M20">
-        <v>0.88347186</v>
+        <v>0.93255363</v>
       </c>
       <c r="N20">
-        <v>5.69652814</v>
+        <v>5.64744637</v>
       </c>
       <c r="O20">
-        <v>1.8228890048</v>
+        <v>1.8071828384</v>
       </c>
       <c r="P20">
-        <v>3.8736391352</v>
+        <v>3.8402635316</v>
       </c>
       <c r="Q20">
-        <v>-2.7063608648</v>
+        <v>-2.7397364684</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1256380506629848</v>
+        <v>0.126349261787338</v>
       </c>
       <c r="T20">
-        <v>1.040557441352652</v>
+        <v>1.049826906497066</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.447888606208691</v>
+        <v>7.055894469039813</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3099,22 +3099,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1093584620477438</v>
+        <v>0.1090474025518401</v>
       </c>
       <c r="C21">
-        <v>81.30684600918589</v>
+        <v>80.88329542885043</v>
       </c>
       <c r="D21">
-        <v>97.66894600918589</v>
+        <v>98.14929542885044</v>
       </c>
       <c r="E21">
-        <v>15.8841</v>
+        <v>16.788</v>
       </c>
       <c r="F21">
-        <v>17.1741</v>
+        <v>18.078</v>
       </c>
       <c r="G21">
         <v>0.8120000000000001</v>
@@ -3135,28 +3135,28 @@
         <v>6.58</v>
       </c>
       <c r="M21">
-        <v>0.93255363</v>
+        <v>0.9816353999999999</v>
       </c>
       <c r="N21">
-        <v>5.64744637</v>
+        <v>5.5983646</v>
       </c>
       <c r="O21">
-        <v>1.8071828384</v>
+        <v>1.791476672</v>
       </c>
       <c r="P21">
-        <v>3.8402635316</v>
+        <v>3.806887928</v>
       </c>
       <c r="Q21">
-        <v>-2.7397364684</v>
+        <v>-2.773112072</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.126349261787338</v>
+        <v>0.1270782531898001</v>
       </c>
       <c r="T21">
-        <v>1.049826906497066</v>
+        <v>1.059328108270091</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3173,7 +3173,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.055894469039813</v>
+        <v>6.703099745587823</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3181,22 +3181,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1090474025518401</v>
+        <v>0.1087363430559363</v>
       </c>
       <c r="C22">
-        <v>80.88329542885043</v>
+        <v>80.46449305093932</v>
       </c>
       <c r="D22">
-        <v>98.14929542885044</v>
+        <v>98.63439305093932</v>
       </c>
       <c r="E22">
-        <v>16.788</v>
+        <v>17.6919</v>
       </c>
       <c r="F22">
-        <v>18.078</v>
+        <v>18.9819</v>
       </c>
       <c r="G22">
         <v>0.8120000000000001</v>
@@ -3217,28 +3217,28 @@
         <v>6.58</v>
       </c>
       <c r="M22">
-        <v>0.9816353999999999</v>
+        <v>1.03071717</v>
       </c>
       <c r="N22">
-        <v>5.5983646</v>
+        <v>5.54928283</v>
       </c>
       <c r="O22">
-        <v>1.791476672</v>
+        <v>1.7757705056</v>
       </c>
       <c r="P22">
-        <v>3.806887928</v>
+        <v>3.7735123244</v>
       </c>
       <c r="Q22">
-        <v>-2.773112072</v>
+        <v>-2.8064876756</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1270782531898001</v>
+        <v>0.1278257000708055</v>
       </c>
       <c r="T22">
-        <v>1.059328108270091</v>
+        <v>1.069069846796864</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3255,7 +3255,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.703099745587823</v>
+        <v>6.383904519607449</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3263,22 +3263,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1087363430559363</v>
+        <v>0.1085748835600326</v>
       </c>
       <c r="C23">
-        <v>80.46449305093932</v>
+        <v>79.81428463071812</v>
       </c>
       <c r="D23">
-        <v>98.63439305093932</v>
+        <v>98.88808463071813</v>
       </c>
       <c r="E23">
-        <v>17.6919</v>
+        <v>18.5958</v>
       </c>
       <c r="F23">
-        <v>18.9819</v>
+        <v>19.8858</v>
       </c>
       <c r="G23">
         <v>0.8120000000000001</v>
@@ -3299,45 +3299,45 @@
         <v>6.58</v>
       </c>
       <c r="M23">
-        <v>1.03071717</v>
+        <v>1.09968474</v>
       </c>
       <c r="N23">
-        <v>5.54928283</v>
+        <v>5.48031526</v>
       </c>
       <c r="O23">
-        <v>1.7757705056</v>
+        <v>1.7537008832</v>
       </c>
       <c r="P23">
-        <v>3.7735123244</v>
+        <v>3.7266143768</v>
       </c>
       <c r="Q23">
-        <v>-2.8064876756</v>
+        <v>-2.8533856232</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1278257000708055</v>
+        <v>0.1285923122564521</v>
       </c>
       <c r="T23">
-        <v>1.069069846796864</v>
+        <v>1.07906137349099</v>
       </c>
       <c r="U23">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V23">
         <v>0.32</v>
       </c>
       <c r="W23">
-        <v>0.036924</v>
+        <v>0.037604</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y23">
-        <v>6.38390451960745</v>
+        <v>5.983533062393864</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3345,22 +3345,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1085748835600326</v>
+        <v>0.1082706240641289</v>
       </c>
       <c r="C24">
-        <v>79.81428463071812</v>
+        <v>79.3920132238588</v>
       </c>
       <c r="D24">
-        <v>98.88808463071813</v>
+        <v>99.3697132238588</v>
       </c>
       <c r="E24">
-        <v>18.5958</v>
+        <v>19.4997</v>
       </c>
       <c r="F24">
-        <v>19.8858</v>
+        <v>20.7897</v>
       </c>
       <c r="G24">
         <v>0.8120000000000001</v>
@@ -3381,28 +3381,28 @@
         <v>6.58</v>
       </c>
       <c r="M24">
-        <v>1.09968474</v>
+        <v>1.14967041</v>
       </c>
       <c r="N24">
-        <v>5.48031526</v>
+        <v>5.430329589999999</v>
       </c>
       <c r="O24">
-        <v>1.7537008832</v>
+        <v>1.7377054688</v>
       </c>
       <c r="P24">
-        <v>3.7266143768</v>
+        <v>3.6926241212</v>
       </c>
       <c r="Q24">
-        <v>-2.8533856232</v>
+        <v>-2.8873758788</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1285923122564521</v>
+        <v>0.1293788364469206</v>
       </c>
       <c r="T24">
-        <v>1.07906137349099</v>
+        <v>1.089312420358988</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3419,7 +3419,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.983533062393864</v>
+        <v>5.723379450985434</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3427,22 +3427,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1082706240641289</v>
+        <v>0.1079663645682252</v>
       </c>
       <c r="C25">
-        <v>79.3920132238588</v>
+        <v>78.97445626584911</v>
       </c>
       <c r="D25">
-        <v>99.3697132238588</v>
+        <v>99.85605626584912</v>
       </c>
       <c r="E25">
-        <v>19.4997</v>
+        <v>20.4036</v>
       </c>
       <c r="F25">
-        <v>20.7897</v>
+        <v>21.6936</v>
       </c>
       <c r="G25">
         <v>0.8120000000000001</v>
@@ -3463,28 +3463,28 @@
         <v>6.58</v>
       </c>
       <c r="M25">
-        <v>1.14967041</v>
+        <v>1.19965608</v>
       </c>
       <c r="N25">
-        <v>5.430329589999999</v>
+        <v>5.38034392</v>
       </c>
       <c r="O25">
-        <v>1.7377054688</v>
+        <v>1.7217100544</v>
       </c>
       <c r="P25">
-        <v>3.6926241212</v>
+        <v>3.6586338656</v>
       </c>
       <c r="Q25">
-        <v>-2.8873758788</v>
+        <v>-2.9213661344</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1293788364469206</v>
+        <v>0.1301860586424015</v>
       </c>
       <c r="T25">
-        <v>1.089312420358988</v>
+        <v>1.09983323161825</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.723379450985434</v>
+        <v>5.484905307194374</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3509,22 +3509,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1079663645682252</v>
+        <v>0.1076621050723214</v>
       </c>
       <c r="C26">
-        <v>78.97445626584911</v>
+        <v>78.56168331862015</v>
       </c>
       <c r="D26">
-        <v>99.85605626584912</v>
+        <v>100.3471833186202</v>
       </c>
       <c r="E26">
-        <v>20.4036</v>
+        <v>21.3075</v>
       </c>
       <c r="F26">
-        <v>21.6936</v>
+        <v>22.5975</v>
       </c>
       <c r="G26">
         <v>0.8120000000000001</v>
@@ -3545,28 +3545,28 @@
         <v>6.58</v>
       </c>
       <c r="M26">
-        <v>1.19965608</v>
+        <v>1.24964175</v>
       </c>
       <c r="N26">
-        <v>5.38034392</v>
+        <v>5.33035825</v>
       </c>
       <c r="O26">
-        <v>1.7217100544</v>
+        <v>1.70571464</v>
       </c>
       <c r="P26">
-        <v>3.6586338656</v>
+        <v>3.62464361</v>
       </c>
       <c r="Q26">
-        <v>-2.9213661344</v>
+        <v>-2.95535639</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1301860586424015</v>
+        <v>0.1310148067630952</v>
       </c>
       <c r="T26">
-        <v>1.09983323161825</v>
+        <v>1.110634597844426</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3583,7 +3583,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.484905307194375</v>
+        <v>5.2655090949066</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3591,22 +3591,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1076621050723214</v>
+        <v>0.1073578455764177</v>
       </c>
       <c r="C27">
-        <v>78.56168331862015</v>
+        <v>78.15376531938691</v>
       </c>
       <c r="D27">
-        <v>100.3471833186202</v>
+        <v>100.8431653193869</v>
       </c>
       <c r="E27">
-        <v>21.3075</v>
+        <v>22.2114</v>
       </c>
       <c r="F27">
-        <v>22.5975</v>
+        <v>23.5014</v>
       </c>
       <c r="G27">
         <v>0.8120000000000001</v>
@@ -3627,28 +3627,28 @@
         <v>6.58</v>
       </c>
       <c r="M27">
-        <v>1.24964175</v>
+        <v>1.29962742</v>
       </c>
       <c r="N27">
-        <v>5.33035825</v>
+        <v>5.28037258</v>
       </c>
       <c r="O27">
-        <v>1.70571464</v>
+        <v>1.6897192256</v>
       </c>
       <c r="P27">
-        <v>3.62464361</v>
+        <v>3.5906533544</v>
       </c>
       <c r="Q27">
-        <v>-2.95535639</v>
+        <v>-2.9893466456</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1310148067630952</v>
+        <v>0.1318659534816455</v>
       </c>
       <c r="T27">
-        <v>1.110634597844426</v>
+        <v>1.121727892887526</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3665,7 +3665,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.2655090949066</v>
+        <v>5.062989514333269</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3673,22 +3673,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1073578455764177</v>
+        <v>0.107053586080514</v>
       </c>
       <c r="C28">
-        <v>78.15376531938691</v>
+        <v>77.75077461480485</v>
       </c>
       <c r="D28">
-        <v>100.8431653193869</v>
+        <v>101.3440746148049</v>
       </c>
       <c r="E28">
-        <v>22.2114</v>
+        <v>23.1153</v>
       </c>
       <c r="F28">
-        <v>23.5014</v>
+        <v>24.4053</v>
       </c>
       <c r="G28">
         <v>0.8120000000000001</v>
@@ -3709,28 +3709,28 @@
         <v>6.58</v>
       </c>
       <c r="M28">
-        <v>1.29962742</v>
+        <v>1.34961309</v>
       </c>
       <c r="N28">
-        <v>5.28037258</v>
+        <v>5.23038691</v>
       </c>
       <c r="O28">
-        <v>1.6897192256</v>
+        <v>1.6737238112</v>
       </c>
       <c r="P28">
-        <v>3.5906533544</v>
+        <v>3.5566630988</v>
       </c>
       <c r="Q28">
-        <v>-2.9893466456</v>
+        <v>-3.0233369012</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1318659534816455</v>
+        <v>0.1327404192883753</v>
       </c>
       <c r="T28">
-        <v>1.121727892887526</v>
+        <v>1.133125113822217</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3747,7 +3747,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.062989514333269</v>
+        <v>4.875471384172778</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3755,22 +3755,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.107053586080514</v>
+        <v>0.1067493265846103</v>
       </c>
       <c r="C29">
-        <v>77.75077461480485</v>
+        <v>77.35278499614967</v>
       </c>
       <c r="D29">
-        <v>101.3440746148049</v>
+        <v>101.8499849961497</v>
       </c>
       <c r="E29">
-        <v>23.1153</v>
+        <v>24.0192</v>
       </c>
       <c r="F29">
-        <v>24.4053</v>
+        <v>25.3092</v>
       </c>
       <c r="G29">
         <v>0.8120000000000001</v>
@@ -3791,28 +3791,28 @@
         <v>6.58</v>
       </c>
       <c r="M29">
-        <v>1.34961309</v>
+        <v>1.39959876</v>
       </c>
       <c r="N29">
-        <v>5.23038691</v>
+        <v>5.18040124</v>
       </c>
       <c r="O29">
-        <v>1.6737238112</v>
+        <v>1.6577283968</v>
       </c>
       <c r="P29">
-        <v>3.5566630988</v>
+        <v>3.5226728432</v>
       </c>
       <c r="Q29">
-        <v>-3.0233369012</v>
+        <v>-3.0573271568</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1327404192883753</v>
+        <v>0.1336391758119587</v>
       </c>
       <c r="T29">
-        <v>1.133125113822217</v>
+        <v>1.144838924227316</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3829,7 +3829,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.875471384172778</v>
+        <v>4.701347406166606</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3837,22 +3837,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1067493265846103</v>
+        <v>0.1064450670887065</v>
       </c>
       <c r="C30">
-        <v>77.35278499614967</v>
+        <v>76.95987173555594</v>
       </c>
       <c r="D30">
-        <v>101.8499849961497</v>
+        <v>102.3609717355559</v>
       </c>
       <c r="E30">
-        <v>24.0192</v>
+        <v>24.92310000000001</v>
       </c>
       <c r="F30">
-        <v>25.3092</v>
+        <v>26.2131</v>
       </c>
       <c r="G30">
         <v>0.8120000000000001</v>
@@ -3873,28 +3873,28 @@
         <v>6.58</v>
       </c>
       <c r="M30">
-        <v>1.39959876</v>
+        <v>1.44958443</v>
       </c>
       <c r="N30">
-        <v>5.18040124</v>
+        <v>5.13041557</v>
       </c>
       <c r="O30">
-        <v>1.6577283968</v>
+        <v>1.6417329824</v>
       </c>
       <c r="P30">
-        <v>3.5226728432</v>
+        <v>3.4886825876</v>
       </c>
       <c r="Q30">
-        <v>-3.0573271568</v>
+        <v>-3.0913174124</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1336391758119587</v>
+        <v>0.1345632494207134</v>
       </c>
       <c r="T30">
-        <v>1.144838924227316</v>
+        <v>1.1568827011227</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3911,7 +3911,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.701347406166606</v>
+        <v>4.539231978367758</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3919,22 +3919,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1064450670887065</v>
+        <v>0.1066508075928028</v>
       </c>
       <c r="C31">
-        <v>76.95987173555595</v>
+        <v>75.70988268994152</v>
       </c>
       <c r="D31">
-        <v>102.3609717355559</v>
+        <v>102.0148826899415</v>
       </c>
       <c r="E31">
-        <v>24.9231</v>
+        <v>25.827</v>
       </c>
       <c r="F31">
-        <v>26.2131</v>
+        <v>27.117</v>
       </c>
       <c r="G31">
         <v>0.8120000000000001</v>
@@ -3955,45 +3955,45 @@
         <v>6.58</v>
       </c>
       <c r="M31">
-        <v>1.44958443</v>
+        <v>1.5673626</v>
       </c>
       <c r="N31">
-        <v>5.13041557</v>
+        <v>5.0126374</v>
       </c>
       <c r="O31">
-        <v>1.6417329824</v>
+        <v>1.604043968</v>
       </c>
       <c r="P31">
-        <v>3.4886825876</v>
+        <v>3.408593432</v>
       </c>
       <c r="Q31">
-        <v>-3.0913174124</v>
+        <v>-3.171406568</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1345632494207134</v>
+        <v>0.1355137251325754</v>
       </c>
       <c r="T31">
-        <v>1.1568827011227</v>
+        <v>1.16927058592938</v>
       </c>
       <c r="U31">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V31">
         <v>0.32</v>
       </c>
       <c r="W31">
-        <v>0.037604</v>
+        <v>0.039304</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y31">
-        <v>4.539231978367759</v>
+        <v>4.198135134779916</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4001,22 +4001,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1066508075928028</v>
+        <v>0.1063635480968991</v>
       </c>
       <c r="C32">
-        <v>75.70988268994152</v>
+        <v>75.28985037433321</v>
       </c>
       <c r="D32">
-        <v>102.0148826899415</v>
+        <v>102.4987503743332</v>
       </c>
       <c r="E32">
-        <v>25.827</v>
+        <v>26.7309</v>
       </c>
       <c r="F32">
-        <v>27.117</v>
+        <v>28.0209</v>
       </c>
       <c r="G32">
         <v>0.8120000000000001</v>
@@ -4037,28 +4037,28 @@
         <v>6.58</v>
       </c>
       <c r="M32">
-        <v>1.5673626</v>
+        <v>1.61960802</v>
       </c>
       <c r="N32">
-        <v>5.0126374</v>
+        <v>4.96039198</v>
       </c>
       <c r="O32">
-        <v>1.604043968</v>
+        <v>1.5873254336</v>
       </c>
       <c r="P32">
-        <v>3.408593432</v>
+        <v>3.3730665464</v>
       </c>
       <c r="Q32">
-        <v>-3.171406568</v>
+        <v>-3.2069334536</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1355137251325754</v>
+        <v>0.1364917508650711</v>
       </c>
       <c r="T32">
-        <v>1.16927058592938</v>
+        <v>1.182017539860892</v>
       </c>
       <c r="U32">
         <v>0.0578</v>
@@ -4075,7 +4075,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.198135134779916</v>
+        <v>4.062711420754757</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1063635480968991</v>
+        <v>0.1068378886009953</v>
       </c>
       <c r="C33">
-        <v>75.28985037433321</v>
+        <v>73.58940727567486</v>
       </c>
       <c r="D33">
-        <v>102.4987503743332</v>
+        <v>101.7022072756749</v>
       </c>
       <c r="E33">
-        <v>26.7309</v>
+        <v>27.6348</v>
       </c>
       <c r="F33">
-        <v>28.0209</v>
+        <v>28.9248</v>
       </c>
       <c r="G33">
         <v>0.8120000000000001</v>
@@ -4119,45 +4119,45 @@
         <v>6.58</v>
       </c>
       <c r="M33">
-        <v>1.61960802</v>
+        <v>1.77309024</v>
       </c>
       <c r="N33">
-        <v>4.96039198</v>
+        <v>4.80690976</v>
       </c>
       <c r="O33">
-        <v>1.5873254336</v>
+        <v>1.5382111232</v>
       </c>
       <c r="P33">
-        <v>3.3730665464</v>
+        <v>3.2686986368</v>
       </c>
       <c r="Q33">
-        <v>-3.2069334536</v>
+        <v>-3.3113013632</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1364917508650711</v>
+        <v>0.1374985420602873</v>
       </c>
       <c r="T33">
-        <v>1.182017539860892</v>
+        <v>1.195139404202154</v>
       </c>
       <c r="U33">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V33">
         <v>0.32</v>
       </c>
       <c r="W33">
-        <v>0.039304</v>
+        <v>0.041684</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>4.062711420754757</v>
+        <v>3.711035034516912</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4165,22 +4165,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1068378886009953</v>
+        <v>0.1065744291050916</v>
       </c>
       <c r="C34">
-        <v>73.58940727567486</v>
+        <v>73.12639026965269</v>
       </c>
       <c r="D34">
-        <v>101.7022072756749</v>
+        <v>102.1430902696527</v>
       </c>
       <c r="E34">
-        <v>27.6348</v>
+        <v>28.5387</v>
       </c>
       <c r="F34">
-        <v>28.9248</v>
+        <v>29.8287</v>
       </c>
       <c r="G34">
         <v>0.8120000000000001</v>
@@ -4201,28 +4201,28 @@
         <v>6.58</v>
       </c>
       <c r="M34">
-        <v>1.77309024</v>
+        <v>1.82849931</v>
       </c>
       <c r="N34">
-        <v>4.80690976</v>
+        <v>4.75150069</v>
       </c>
       <c r="O34">
-        <v>1.5382111232</v>
+        <v>1.5204802208</v>
       </c>
       <c r="P34">
-        <v>3.2686986368</v>
+        <v>3.2310204692</v>
       </c>
       <c r="Q34">
-        <v>-3.3113013632</v>
+        <v>-3.3489795308</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1374985420602873</v>
+        <v>0.1385353867240174</v>
       </c>
       <c r="T34">
-        <v>1.195139404202154</v>
+        <v>1.208652965986439</v>
       </c>
       <c r="U34">
         <v>0.0613</v>
@@ -4239,7 +4239,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.711035034516912</v>
+        <v>3.598579427410339</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4247,22 +4247,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1065744291050916</v>
+        <v>0.1069583296091879</v>
       </c>
       <c r="C35">
-        <v>73.12639026965269</v>
+        <v>71.58132194319499</v>
       </c>
       <c r="D35">
-        <v>102.1430902696527</v>
+        <v>101.501921943195</v>
       </c>
       <c r="E35">
-        <v>28.5387</v>
+        <v>29.4426</v>
       </c>
       <c r="F35">
-        <v>29.8287</v>
+        <v>30.7326</v>
       </c>
       <c r="G35">
         <v>0.8120000000000001</v>
@@ -4283,45 +4283,45 @@
         <v>6.58</v>
       </c>
       <c r="M35">
-        <v>1.82849931</v>
+        <v>1.96995966</v>
       </c>
       <c r="N35">
-        <v>4.75150069</v>
+        <v>4.610040339999999</v>
       </c>
       <c r="O35">
-        <v>1.5204802208</v>
+        <v>1.4752129088</v>
       </c>
       <c r="P35">
-        <v>3.2310204692</v>
+        <v>3.1348274312</v>
       </c>
       <c r="Q35">
-        <v>-3.3489795308</v>
+        <v>-3.4451725688</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1385353867240174</v>
+        <v>0.139603650923012</v>
       </c>
       <c r="T35">
-        <v>1.208652965986439</v>
+        <v>1.222576029642975</v>
       </c>
       <c r="U35">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V35">
         <v>0.32</v>
       </c>
       <c r="W35">
-        <v>0.041684</v>
+        <v>0.043588</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y35">
-        <v>3.598579427410339</v>
+        <v>3.340169920027702</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4329,22 +4329,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1069583296091879</v>
+        <v>0.1067139101132842</v>
       </c>
       <c r="C36">
-        <v>71.58132194319499</v>
+        <v>71.08470245676695</v>
       </c>
       <c r="D36">
-        <v>101.501921943195</v>
+        <v>101.9092024567669</v>
       </c>
       <c r="E36">
-        <v>29.4426</v>
+        <v>30.3465</v>
       </c>
       <c r="F36">
-        <v>30.7326</v>
+        <v>31.6365</v>
       </c>
       <c r="G36">
         <v>0.8120000000000001</v>
@@ -4365,28 +4365,28 @@
         <v>6.58</v>
       </c>
       <c r="M36">
-        <v>1.96995966</v>
+        <v>2.02789965</v>
       </c>
       <c r="N36">
-        <v>4.610040339999999</v>
+        <v>4.55210035</v>
       </c>
       <c r="O36">
-        <v>1.4752129088</v>
+        <v>1.456672112</v>
       </c>
       <c r="P36">
-        <v>3.1348274312</v>
+        <v>3.095428238</v>
       </c>
       <c r="Q36">
-        <v>-3.4451725688</v>
+        <v>-3.484571762</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.139603650923012</v>
+        <v>0.140704784789668</v>
       </c>
       <c r="T36">
-        <v>1.222576029642975</v>
+        <v>1.236927495258174</v>
       </c>
       <c r="U36">
         <v>0.0641</v>
@@ -4403,7 +4403,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.340169920027702</v>
+        <v>3.244736493741196</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4411,22 +4411,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1067139101132842</v>
+        <v>0.1064694906173804</v>
       </c>
       <c r="C37">
-        <v>71.08470245676695</v>
+        <v>70.59136459663267</v>
       </c>
       <c r="D37">
-        <v>101.9092024567669</v>
+        <v>102.3197645966327</v>
       </c>
       <c r="E37">
-        <v>30.3465</v>
+        <v>31.25040000000001</v>
       </c>
       <c r="F37">
-        <v>31.6365</v>
+        <v>32.54040000000001</v>
       </c>
       <c r="G37">
         <v>0.8120000000000001</v>
@@ -4447,28 +4447,28 @@
         <v>6.58</v>
       </c>
       <c r="M37">
-        <v>2.02789965</v>
+        <v>2.085839640000001</v>
       </c>
       <c r="N37">
-        <v>4.55210035</v>
+        <v>4.49416036</v>
       </c>
       <c r="O37">
-        <v>1.456672112</v>
+        <v>1.4381313152</v>
       </c>
       <c r="P37">
-        <v>3.095428238</v>
+        <v>3.0560290448</v>
       </c>
       <c r="Q37">
-        <v>-3.484571762</v>
+        <v>-3.5239709552</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.140704784789668</v>
+        <v>0.1418403290896569</v>
       </c>
       <c r="T37">
-        <v>1.236927495258174</v>
+        <v>1.251727444173847</v>
       </c>
       <c r="U37">
         <v>0.0641</v>
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.244736493741196</v>
+        <v>3.154604924470607</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4493,22 +4493,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1064694906173804</v>
+        <v>0.1062250711214767</v>
       </c>
       <c r="C38">
-        <v>70.59136459663264</v>
+        <v>70.10134818534073</v>
       </c>
       <c r="D38">
-        <v>102.3197645966327</v>
+        <v>102.7336481853407</v>
       </c>
       <c r="E38">
-        <v>31.2504</v>
+        <v>32.1543</v>
       </c>
       <c r="F38">
-        <v>32.5404</v>
+        <v>33.4443</v>
       </c>
       <c r="G38">
         <v>0.8120000000000001</v>
@@ -4529,28 +4529,28 @@
         <v>6.58</v>
       </c>
       <c r="M38">
-        <v>2.08583964</v>
+        <v>2.14377963</v>
       </c>
       <c r="N38">
-        <v>4.49416036</v>
+        <v>4.43622037</v>
       </c>
       <c r="O38">
-        <v>1.4381313152</v>
+        <v>1.4195905184</v>
       </c>
       <c r="P38">
-        <v>3.0560290448</v>
+        <v>3.0166298516</v>
       </c>
       <c r="Q38">
-        <v>-3.5239709552</v>
+        <v>-3.5633701484</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1418403290896569</v>
+        <v>0.1430119224150424</v>
       </c>
       <c r="T38">
-        <v>1.251727444173847</v>
+        <v>1.266997232737637</v>
       </c>
       <c r="U38">
         <v>0.0641</v>
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.154604924470608</v>
+        <v>3.069345331917348</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4575,22 +4575,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1062250711214767</v>
+        <v>0.107996171625573</v>
       </c>
       <c r="C39">
-        <v>70.10134818534073</v>
+        <v>66.27200098604891</v>
       </c>
       <c r="D39">
-        <v>102.7336481853407</v>
+        <v>99.8082009860489</v>
       </c>
       <c r="E39">
-        <v>32.1543</v>
+        <v>33.0582</v>
       </c>
       <c r="F39">
-        <v>33.4443</v>
+        <v>34.3482</v>
       </c>
       <c r="G39">
         <v>0.8120000000000001</v>
@@ -4611,45 +4611,45 @@
         <v>6.58</v>
       </c>
       <c r="M39">
-        <v>2.14377963</v>
+        <v>2.46963558</v>
       </c>
       <c r="N39">
-        <v>4.43622037</v>
+        <v>4.11036442</v>
       </c>
       <c r="O39">
-        <v>1.4195905184</v>
+        <v>1.3153166144</v>
       </c>
       <c r="P39">
-        <v>3.0166298516</v>
+        <v>2.7950478056</v>
       </c>
       <c r="Q39">
-        <v>-3.5633701484</v>
+        <v>-3.7849521944</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1430119224150424</v>
+        <v>0.1442213090735048</v>
       </c>
       <c r="T39">
-        <v>1.266997232737637</v>
+        <v>1.282759595126066</v>
       </c>
       <c r="U39">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V39">
         <v>0.32</v>
       </c>
       <c r="W39">
-        <v>0.043588</v>
+        <v>0.048892</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y39">
-        <v>3.069345331917348</v>
+        <v>2.664360707015729</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4657,22 +4657,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.107996171625573</v>
+        <v>0.1078047921296693</v>
       </c>
       <c r="C40">
-        <v>66.27200098604891</v>
+        <v>65.6761617428985</v>
       </c>
       <c r="D40">
-        <v>99.8082009860489</v>
+        <v>100.1162617428985</v>
       </c>
       <c r="E40">
-        <v>33.0582</v>
+        <v>33.9621</v>
       </c>
       <c r="F40">
-        <v>34.3482</v>
+        <v>35.2521</v>
       </c>
       <c r="G40">
         <v>0.8120000000000001</v>
@@ -4693,28 +4693,28 @@
         <v>6.58</v>
       </c>
       <c r="M40">
-        <v>2.46963558</v>
+        <v>2.53462599</v>
       </c>
       <c r="N40">
-        <v>4.11036442</v>
+        <v>4.04537401</v>
       </c>
       <c r="O40">
-        <v>1.3153166144</v>
+        <v>1.2945196832</v>
       </c>
       <c r="P40">
-        <v>2.7950478056</v>
+        <v>2.7508543268</v>
       </c>
       <c r="Q40">
-        <v>-3.7849521944</v>
+        <v>-3.8291456732</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1442213090735048</v>
+        <v>0.1454703477535562</v>
       </c>
       <c r="T40">
-        <v>1.282759595126066</v>
+        <v>1.299038756281328</v>
       </c>
       <c r="U40">
         <v>0.07190000000000001</v>
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.664360707015729</v>
+        <v>2.596043765810197</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4739,22 +4739,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1078047921296693</v>
+        <v>0.1076134126337655</v>
       </c>
       <c r="C41">
-        <v>65.6761617428985</v>
+        <v>65.08223006349004</v>
       </c>
       <c r="D41">
-        <v>100.1162617428985</v>
+        <v>100.4262300634901</v>
       </c>
       <c r="E41">
-        <v>33.9621</v>
+        <v>34.866</v>
       </c>
       <c r="F41">
-        <v>35.2521</v>
+        <v>36.156</v>
       </c>
       <c r="G41">
         <v>0.8120000000000001</v>
@@ -4775,28 +4775,28 @@
         <v>6.58</v>
       </c>
       <c r="M41">
-        <v>2.53462599</v>
+        <v>2.5996164</v>
       </c>
       <c r="N41">
-        <v>4.04537401</v>
+        <v>3.9803836</v>
       </c>
       <c r="O41">
-        <v>1.2945196832</v>
+        <v>1.273722752</v>
       </c>
       <c r="P41">
-        <v>2.7508543268</v>
+        <v>2.706660848</v>
       </c>
       <c r="Q41">
-        <v>-3.8291456732</v>
+        <v>-3.873339152</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1454703477535562</v>
+        <v>0.1467610210562759</v>
       </c>
       <c r="T41">
-        <v>1.299038756281328</v>
+        <v>1.315860556141766</v>
       </c>
       <c r="U41">
         <v>0.07190000000000001</v>
@@ -4813,7 +4813,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.596043765810197</v>
+        <v>2.531142671664942</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4821,22 +4821,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1076134126337655</v>
+        <v>0.1085093531378618</v>
       </c>
       <c r="C42">
-        <v>65.08223006349004</v>
+        <v>62.74352133583877</v>
       </c>
       <c r="D42">
-        <v>100.4262300634901</v>
+        <v>98.99142133583878</v>
       </c>
       <c r="E42">
-        <v>34.866</v>
+        <v>35.76990000000001</v>
       </c>
       <c r="F42">
-        <v>36.156</v>
+        <v>37.05990000000001</v>
       </c>
       <c r="G42">
         <v>0.8120000000000001</v>
@@ -4857,45 +4857,45 @@
         <v>6.58</v>
       </c>
       <c r="M42">
-        <v>2.5996164</v>
+        <v>2.809140420000001</v>
       </c>
       <c r="N42">
-        <v>3.9803836</v>
+        <v>3.770859579999999</v>
       </c>
       <c r="O42">
-        <v>1.273722752</v>
+        <v>1.2066750656</v>
       </c>
       <c r="P42">
-        <v>2.706660848</v>
+        <v>2.5641845144</v>
       </c>
       <c r="Q42">
-        <v>-3.873339152</v>
+        <v>-4.015815485600001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1467610210562759</v>
+        <v>0.1480954459963759</v>
       </c>
       <c r="T42">
-        <v>1.315860556141766</v>
+        <v>1.333252586505947</v>
       </c>
       <c r="U42">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V42">
         <v>0.32</v>
       </c>
       <c r="W42">
-        <v>0.048892</v>
+        <v>0.051544</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y42">
-        <v>2.531142671664942</v>
+        <v>2.342353537456842</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4903,22 +4903,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1085093531378618</v>
+        <v>0.1083444936419581</v>
       </c>
       <c r="C43">
-        <v>62.74352133583877</v>
+        <v>62.10055039401681</v>
       </c>
       <c r="D43">
-        <v>98.99142133583878</v>
+        <v>99.25235039401682</v>
       </c>
       <c r="E43">
-        <v>35.76990000000001</v>
+        <v>36.67380000000001</v>
       </c>
       <c r="F43">
-        <v>37.05990000000001</v>
+        <v>37.96380000000001</v>
       </c>
       <c r="G43">
         <v>0.8120000000000001</v>
@@ -4939,28 +4939,28 @@
         <v>6.58</v>
       </c>
       <c r="M43">
-        <v>2.809140420000001</v>
+        <v>2.877656040000001</v>
       </c>
       <c r="N43">
-        <v>3.770859579999999</v>
+        <v>3.702343959999999</v>
       </c>
       <c r="O43">
-        <v>1.2066750656</v>
+        <v>1.1847500672</v>
       </c>
       <c r="P43">
-        <v>2.5641845144</v>
+        <v>2.5175938928</v>
       </c>
       <c r="Q43">
-        <v>-4.015815485600001</v>
+        <v>-4.0624061072</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1480954459963759</v>
+        <v>0.1494758855895829</v>
       </c>
       <c r="T43">
-        <v>1.333252586505947</v>
+        <v>1.3512443420551</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4977,7 +4977,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.342353537456842</v>
+        <v>2.286583215136441</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4985,22 +4985,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1083444936419581</v>
+        <v>0.1081796341460544</v>
       </c>
       <c r="C44">
-        <v>62.1005503940168</v>
+        <v>61.45895864056577</v>
       </c>
       <c r="D44">
-        <v>99.2523503940168</v>
+        <v>99.51465864056577</v>
       </c>
       <c r="E44">
-        <v>36.6738</v>
+        <v>37.5777</v>
       </c>
       <c r="F44">
-        <v>37.9638</v>
+        <v>38.8677</v>
       </c>
       <c r="G44">
         <v>0.8120000000000001</v>
@@ -5021,28 +5021,28 @@
         <v>6.58</v>
       </c>
       <c r="M44">
-        <v>2.87765604</v>
+        <v>2.94617166</v>
       </c>
       <c r="N44">
-        <v>3.70234396</v>
+        <v>3.63382834</v>
       </c>
       <c r="O44">
-        <v>1.1847500672</v>
+        <v>1.1628250688</v>
       </c>
       <c r="P44">
-        <v>2.5175938928</v>
+        <v>2.4710032712</v>
       </c>
       <c r="Q44">
-        <v>-4.0624061072</v>
+        <v>-4.1089967288</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1494758855895829</v>
+        <v>0.1509047616597445</v>
       </c>
       <c r="T44">
-        <v>1.3512443420551</v>
+        <v>1.369867387272645</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -5059,7 +5059,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.286583215136441</v>
+        <v>2.233406861296059</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5067,22 +5067,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1081796341460544</v>
+        <v>0.1080147746501506</v>
       </c>
       <c r="C45">
-        <v>61.45895864056577</v>
+        <v>60.81875703939098</v>
       </c>
       <c r="D45">
-        <v>99.51465864056577</v>
+        <v>99.77835703939098</v>
       </c>
       <c r="E45">
-        <v>37.5777</v>
+        <v>38.4816</v>
       </c>
       <c r="F45">
-        <v>38.8677</v>
+        <v>39.7716</v>
       </c>
       <c r="G45">
         <v>0.8120000000000001</v>
@@ -5103,28 +5103,28 @@
         <v>6.58</v>
       </c>
       <c r="M45">
-        <v>2.94617166</v>
+        <v>3.01468728</v>
       </c>
       <c r="N45">
-        <v>3.63382834</v>
+        <v>3.56531272</v>
       </c>
       <c r="O45">
-        <v>1.1628250688</v>
+        <v>1.1409000704</v>
       </c>
       <c r="P45">
-        <v>2.4710032712</v>
+        <v>2.4244126496</v>
       </c>
       <c r="Q45">
-        <v>-4.1089967288</v>
+        <v>-4.1555873504</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1509047616597445</v>
+        <v>0.1523846690181261</v>
       </c>
       <c r="T45">
-        <v>1.369867387272645</v>
+        <v>1.389155541247959</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5141,7 +5141,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.233406861296059</v>
+        <v>2.182647614448421</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1080147746501506</v>
+        <v>0.1078499151542469</v>
       </c>
       <c r="C46">
-        <v>60.81875703939098</v>
+        <v>60.17995667091705</v>
       </c>
       <c r="D46">
-        <v>99.77835703939098</v>
+        <v>100.0434566709171</v>
       </c>
       <c r="E46">
-        <v>38.4816</v>
+        <v>39.3855</v>
       </c>
       <c r="F46">
-        <v>39.7716</v>
+        <v>40.6755</v>
       </c>
       <c r="G46">
         <v>0.8120000000000001</v>
@@ -5185,28 +5185,28 @@
         <v>6.58</v>
       </c>
       <c r="M46">
-        <v>3.01468728</v>
+        <v>3.0832029</v>
       </c>
       <c r="N46">
-        <v>3.56531272</v>
+        <v>3.4967971</v>
       </c>
       <c r="O46">
-        <v>1.1409000704</v>
+        <v>1.118975072</v>
       </c>
       <c r="P46">
-        <v>2.4244126496</v>
+        <v>2.377822028</v>
       </c>
       <c r="Q46">
-        <v>-4.1555873504</v>
+        <v>-4.202177972</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1523846690181261</v>
+        <v>0.1539183911895398</v>
       </c>
       <c r="T46">
-        <v>1.389155541247959</v>
+        <v>1.409145082640556</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5223,7 +5223,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.182647614448421</v>
+        <v>2.134144334127345</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5231,22 +5231,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1078499151542469</v>
+        <v>0.1076850556583432</v>
       </c>
       <c r="C47">
-        <v>60.17995667091705</v>
+        <v>59.54256873364006</v>
       </c>
       <c r="D47">
-        <v>100.0434566709171</v>
+        <v>100.3099687336401</v>
       </c>
       <c r="E47">
-        <v>39.3855</v>
+        <v>40.2894</v>
       </c>
       <c r="F47">
-        <v>40.6755</v>
+        <v>41.5794</v>
       </c>
       <c r="G47">
         <v>0.8120000000000001</v>
@@ -5267,28 +5267,28 @@
         <v>6.58</v>
       </c>
       <c r="M47">
-        <v>3.0832029</v>
+        <v>3.15171852</v>
       </c>
       <c r="N47">
-        <v>3.4967971</v>
+        <v>3.42828148</v>
       </c>
       <c r="O47">
-        <v>1.118975072</v>
+        <v>1.0970500736</v>
       </c>
       <c r="P47">
-        <v>2.377822028</v>
+        <v>2.3312314064</v>
       </c>
       <c r="Q47">
-        <v>-4.202177972</v>
+        <v>-4.2487685936</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1539183911895398</v>
+        <v>0.1555089178858207</v>
       </c>
       <c r="T47">
-        <v>1.409145082640556</v>
+        <v>1.429874977418066</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5305,7 +5305,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.134144334127345</v>
+        <v>2.087749892081098</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5313,22 +5313,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1076850556583432</v>
+        <v>0.1075201961624394</v>
       </c>
       <c r="C48">
-        <v>59.54256873364006</v>
+        <v>58.90660454570431</v>
       </c>
       <c r="D48">
-        <v>100.3099687336401</v>
+        <v>100.5779045457043</v>
       </c>
       <c r="E48">
-        <v>40.2894</v>
+        <v>41.1933</v>
       </c>
       <c r="F48">
-        <v>41.5794</v>
+        <v>42.4833</v>
       </c>
       <c r="G48">
         <v>0.8120000000000001</v>
@@ -5349,28 +5349,28 @@
         <v>6.58</v>
       </c>
       <c r="M48">
-        <v>3.15171852</v>
+        <v>3.22023414</v>
       </c>
       <c r="N48">
-        <v>3.42828148</v>
+        <v>3.35976586</v>
       </c>
       <c r="O48">
-        <v>1.0970500736</v>
+        <v>1.0751250752</v>
       </c>
       <c r="P48">
-        <v>2.3312314064</v>
+        <v>2.2846407848</v>
       </c>
       <c r="Q48">
-        <v>-4.2487685936</v>
+        <v>-4.2953592152</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1555089178858207</v>
+        <v>0.1571594644574329</v>
       </c>
       <c r="T48">
-        <v>1.429874977418066</v>
+        <v>1.451387132375858</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5387,7 +5387,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.087749892081098</v>
+        <v>2.043329681611288</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5395,22 +5395,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1075201961624394</v>
+        <v>0.1073553366665357</v>
       </c>
       <c r="C49">
-        <v>58.90660454570431</v>
+        <v>58.2720755465045</v>
       </c>
       <c r="D49">
-        <v>100.5779045457043</v>
+        <v>100.8472755465045</v>
       </c>
       <c r="E49">
-        <v>41.1933</v>
+        <v>42.09720000000001</v>
       </c>
       <c r="F49">
-        <v>42.4833</v>
+        <v>43.38720000000001</v>
       </c>
       <c r="G49">
         <v>0.8120000000000001</v>
@@ -5431,28 +5431,28 @@
         <v>6.58</v>
       </c>
       <c r="M49">
-        <v>3.22023414</v>
+        <v>3.288749760000001</v>
       </c>
       <c r="N49">
-        <v>3.35976586</v>
+        <v>3.291250239999999</v>
       </c>
       <c r="O49">
-        <v>1.0751250752</v>
+        <v>1.0532000768</v>
       </c>
       <c r="P49">
-        <v>2.2846407848</v>
+        <v>2.2380501632</v>
       </c>
       <c r="Q49">
-        <v>-4.2953592152</v>
+        <v>-4.3419498368</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1571594644574329</v>
+        <v>0.1588734935894918</v>
       </c>
       <c r="T49">
-        <v>1.451387132375858</v>
+        <v>1.47372667790895</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5469,7 +5469,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.043329681611288</v>
+        <v>2.000760313244386</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5477,22 +5477,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1073553366665357</v>
+        <v>0.111921917170632</v>
       </c>
       <c r="C50">
-        <v>58.27207554650453</v>
+        <v>50.40335628372557</v>
       </c>
       <c r="D50">
-        <v>100.8472755465045</v>
+        <v>93.88245628372557</v>
       </c>
       <c r="E50">
-        <v>42.0972</v>
+        <v>43.0011</v>
       </c>
       <c r="F50">
-        <v>43.3872</v>
+        <v>44.2911</v>
       </c>
       <c r="G50">
         <v>0.8120000000000001</v>
@@ -5513,45 +5513,45 @@
         <v>6.58</v>
       </c>
       <c r="M50">
-        <v>3.28874976</v>
+        <v>3.986199</v>
       </c>
       <c r="N50">
-        <v>3.29125024</v>
+        <v>2.593801</v>
       </c>
       <c r="O50">
-        <v>1.0532000768</v>
+        <v>0.83001632</v>
       </c>
       <c r="P50">
-        <v>2.2380501632</v>
+        <v>1.76378468</v>
       </c>
       <c r="Q50">
-        <v>-4.3419498368</v>
+        <v>-4.81621532</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1588734935894918</v>
+        <v>0.1606547395502588</v>
       </c>
       <c r="T50">
-        <v>1.47372667790895</v>
+        <v>1.496942284051183</v>
       </c>
       <c r="U50">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V50">
         <v>0.32</v>
       </c>
       <c r="W50">
-        <v>0.051544</v>
+        <v>0.06119999999999999</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y50">
-        <v>2.000760313244386</v>
+        <v>1.650695311498498</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5559,22 +5559,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.111921917170632</v>
+        <v>0.1118536176747283</v>
       </c>
       <c r="C51">
-        <v>50.40335628372557</v>
+        <v>49.59653082201894</v>
       </c>
       <c r="D51">
-        <v>93.88245628372557</v>
+        <v>93.97953082201894</v>
       </c>
       <c r="E51">
-        <v>43.0011</v>
+        <v>43.905</v>
       </c>
       <c r="F51">
-        <v>44.2911</v>
+        <v>45.195</v>
       </c>
       <c r="G51">
         <v>0.8120000000000001</v>
@@ -5595,28 +5595,28 @@
         <v>6.58</v>
       </c>
       <c r="M51">
-        <v>3.986199</v>
+        <v>4.06755</v>
       </c>
       <c r="N51">
-        <v>2.593801</v>
+        <v>2.51245</v>
       </c>
       <c r="O51">
-        <v>0.83001632</v>
+        <v>0.8039840000000001</v>
       </c>
       <c r="P51">
-        <v>1.76378468</v>
+        <v>1.708466</v>
       </c>
       <c r="Q51">
-        <v>-4.81621532</v>
+        <v>-4.871534</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1606547395502588</v>
+        <v>0.1625072353494565</v>
       </c>
       <c r="T51">
-        <v>1.496942284051183</v>
+        <v>1.521086514439105</v>
       </c>
       <c r="U51">
         <v>0.09</v>
@@ -5633,7 +5633,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.650695311498498</v>
+        <v>1.617681405268528</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5641,22 +5641,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1118536176747283</v>
+        <v>0.1117853181788245</v>
       </c>
       <c r="C52">
-        <v>49.59653082201894</v>
+        <v>48.78990631841069</v>
       </c>
       <c r="D52">
-        <v>93.97953082201894</v>
+        <v>94.07680631841069</v>
       </c>
       <c r="E52">
-        <v>43.905</v>
+        <v>44.8089</v>
       </c>
       <c r="F52">
-        <v>45.195</v>
+        <v>46.0989</v>
       </c>
       <c r="G52">
         <v>0.8120000000000001</v>
@@ -5677,28 +5677,28 @@
         <v>6.58</v>
       </c>
       <c r="M52">
-        <v>4.06755</v>
+        <v>4.148901</v>
       </c>
       <c r="N52">
-        <v>2.51245</v>
+        <v>2.431099000000001</v>
       </c>
       <c r="O52">
-        <v>0.8039840000000001</v>
+        <v>0.7779516800000001</v>
       </c>
       <c r="P52">
-        <v>1.708466</v>
+        <v>1.65314732</v>
       </c>
       <c r="Q52">
-        <v>-4.871534</v>
+        <v>-4.92685268</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1625072353494565</v>
+        <v>0.1644353432220909</v>
       </c>
       <c r="T52">
-        <v>1.521086514439105</v>
+        <v>1.546216223618372</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5715,7 +5715,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.617681405268528</v>
+        <v>1.585962162027969</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5723,22 +5723,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1117853181788245</v>
+        <v>0.1117170186829208</v>
       </c>
       <c r="C53">
-        <v>48.78990631841069</v>
+        <v>47.9834833975651</v>
       </c>
       <c r="D53">
-        <v>94.07680631841069</v>
+        <v>94.17428339756511</v>
       </c>
       <c r="E53">
-        <v>44.8089</v>
+        <v>45.7128</v>
       </c>
       <c r="F53">
-        <v>46.0989</v>
+        <v>47.0028</v>
       </c>
       <c r="G53">
         <v>0.8120000000000001</v>
@@ -5759,28 +5759,28 @@
         <v>6.58</v>
       </c>
       <c r="M53">
-        <v>4.148901</v>
+        <v>4.230252</v>
       </c>
       <c r="N53">
-        <v>2.431099000000001</v>
+        <v>2.349748</v>
       </c>
       <c r="O53">
-        <v>0.7779516800000001</v>
+        <v>0.75191936</v>
       </c>
       <c r="P53">
-        <v>1.65314732</v>
+        <v>1.59782864</v>
       </c>
       <c r="Q53">
-        <v>-4.92685268</v>
+        <v>-4.982171360000001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1644353432220909</v>
+        <v>0.1664437889227517</v>
       </c>
       <c r="T53">
-        <v>1.546216223618372</v>
+        <v>1.572393004013441</v>
       </c>
       <c r="U53">
         <v>0.09</v>
@@ -5797,7 +5797,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.585962162027969</v>
+        <v>1.555462889681277</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5805,22 +5805,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1117170186829208</v>
+        <v>0.1116487191870171</v>
       </c>
       <c r="C54">
-        <v>47.9834833975651</v>
+        <v>47.17726268673822</v>
       </c>
       <c r="D54">
-        <v>94.17428339756511</v>
+        <v>94.27196268673822</v>
       </c>
       <c r="E54">
-        <v>45.7128</v>
+        <v>46.6167</v>
       </c>
       <c r="F54">
-        <v>47.0028</v>
+        <v>47.9067</v>
       </c>
       <c r="G54">
         <v>0.8120000000000001</v>
@@ -5841,28 +5841,28 @@
         <v>6.58</v>
       </c>
       <c r="M54">
-        <v>4.230252</v>
+        <v>4.311603</v>
       </c>
       <c r="N54">
-        <v>2.349748</v>
+        <v>2.268397</v>
       </c>
       <c r="O54">
-        <v>0.75191936</v>
+        <v>0.72588704</v>
       </c>
       <c r="P54">
-        <v>1.59782864</v>
+        <v>1.54250996</v>
       </c>
       <c r="Q54">
-        <v>-4.982171360000001</v>
+        <v>-5.03749004</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1664437889227517</v>
+        <v>0.1685377003979087</v>
       </c>
       <c r="T54">
-        <v>1.572393004013441</v>
+        <v>1.599683689957236</v>
       </c>
       <c r="U54">
         <v>0.09</v>
@@ -5879,7 +5879,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.555462889681277</v>
+        <v>1.526114533272196</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5887,22 +5887,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1116487191870171</v>
+        <v>0.1354905202602187</v>
       </c>
       <c r="C55">
-        <v>47.17726268673822</v>
+        <v>21.2137089503511</v>
       </c>
       <c r="D55">
-        <v>94.27196268673822</v>
+        <v>69.2123089503511</v>
       </c>
       <c r="E55">
-        <v>46.6167</v>
+        <v>47.5206</v>
       </c>
       <c r="F55">
-        <v>47.9067</v>
+        <v>48.8106</v>
       </c>
       <c r="G55">
         <v>0.8120000000000001</v>
@@ -5923,45 +5923,45 @@
         <v>6.58</v>
       </c>
       <c r="M55">
-        <v>4.311603</v>
+        <v>7.165396080000001</v>
       </c>
       <c r="N55">
-        <v>2.268397</v>
+        <v>-0.5853960800000007</v>
       </c>
       <c r="O55">
-        <v>0.72588704</v>
+        <v>-0.1873267456000002</v>
       </c>
       <c r="P55">
-        <v>1.54250996</v>
+        <v>-0.3980693344000005</v>
       </c>
       <c r="Q55">
-        <v>-5.03749004</v>
+        <v>-6.978069334400001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1685377003979087</v>
+        <v>0.1728546358610554</v>
       </c>
       <c r="T55">
-        <v>1.599683689957236</v>
+        <v>1.655947830711101</v>
       </c>
       <c r="U55">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.32</v>
+        <v>0.2938567493675799</v>
       </c>
       <c r="W55">
-        <v>0.06119999999999999</v>
+        <v>0.1036618291928393</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y55">
-        <v>1.526114533272196</v>
+        <v>0.9183023417736873</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5969,22 +5969,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1354905202602187</v>
+        <v>0.1365005202602187</v>
       </c>
       <c r="C56">
-        <v>21.2137089503511</v>
+        <v>19.53909195954114</v>
       </c>
       <c r="D56">
-        <v>69.2123089503511</v>
+        <v>68.44159195954114</v>
       </c>
       <c r="E56">
-        <v>47.5206</v>
+        <v>48.4245</v>
       </c>
       <c r="F56">
-        <v>48.8106</v>
+        <v>49.7145</v>
       </c>
       <c r="G56">
         <v>0.8120000000000001</v>
@@ -6005,37 +6005,37 @@
         <v>6.58</v>
       </c>
       <c r="M56">
-        <v>7.165396080000001</v>
+        <v>7.298088600000001</v>
       </c>
       <c r="N56">
-        <v>-0.5853960800000007</v>
+        <v>-0.7180886000000006</v>
       </c>
       <c r="O56">
-        <v>-0.1873267456000002</v>
+        <v>-0.2297883520000002</v>
       </c>
       <c r="P56">
-        <v>-0.3980693344000005</v>
+        <v>-0.4883002480000004</v>
       </c>
       <c r="Q56">
-        <v>-6.978069334400001</v>
+        <v>-7.068300248000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1728546358610554</v>
+        <v>0.1756780722135233</v>
       </c>
       <c r="T56">
-        <v>1.655947830711101</v>
+        <v>1.69274667139357</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.2938567493675799</v>
+        <v>0.2885138993790785</v>
       </c>
       <c r="W56">
-        <v>0.1036618291928393</v>
+        <v>0.1044461595711513</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6043,7 +6043,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.9183023417736873</v>
+        <v>0.9016059355596203</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6051,22 +6051,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1365005202602187</v>
+        <v>0.1375105202602187</v>
       </c>
       <c r="C57">
-        <v>19.53909195954114</v>
+        <v>17.8814506473885</v>
       </c>
       <c r="D57">
-        <v>68.44159195954114</v>
+        <v>67.68785064738852</v>
       </c>
       <c r="E57">
-        <v>48.4245</v>
+        <v>49.32840000000001</v>
       </c>
       <c r="F57">
-        <v>49.7145</v>
+        <v>50.61840000000001</v>
       </c>
       <c r="G57">
         <v>0.8120000000000001</v>
@@ -6087,37 +6087,37 @@
         <v>6.58</v>
       </c>
       <c r="M57">
-        <v>7.298088600000001</v>
+        <v>7.430781120000002</v>
       </c>
       <c r="N57">
-        <v>-0.7180886000000006</v>
+        <v>-0.8507811200000015</v>
       </c>
       <c r="O57">
-        <v>-0.2297883520000002</v>
+        <v>-0.2722499584000005</v>
       </c>
       <c r="P57">
-        <v>-0.4883002480000004</v>
+        <v>-0.5785311616000011</v>
       </c>
       <c r="Q57">
-        <v>-7.068300248000001</v>
+        <v>-7.158531161600001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1756780722135233</v>
+        <v>0.1786298465820124</v>
       </c>
       <c r="T57">
-        <v>1.69274667139357</v>
+        <v>1.731218186652515</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.2885138993790785</v>
+        <v>0.2833618654615949</v>
       </c>
       <c r="W57">
-        <v>0.1044461595711513</v>
+        <v>0.1052024781502379</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.9016059355596203</v>
+        <v>0.8855058295674841</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6133,22 +6133,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1375105202602187</v>
+        <v>0.1385205202602187</v>
       </c>
       <c r="C58">
-        <v>17.8814506473885</v>
+        <v>16.24023026823189</v>
       </c>
       <c r="D58">
-        <v>67.68785064738852</v>
+        <v>66.9505302682319</v>
       </c>
       <c r="E58">
-        <v>49.32840000000001</v>
+        <v>50.23230000000001</v>
       </c>
       <c r="F58">
-        <v>50.61840000000001</v>
+        <v>51.52230000000001</v>
       </c>
       <c r="G58">
         <v>0.8120000000000001</v>
@@ -6169,37 +6169,37 @@
         <v>6.58</v>
       </c>
       <c r="M58">
-        <v>7.430781120000002</v>
+        <v>7.563473640000002</v>
       </c>
       <c r="N58">
-        <v>-0.8507811200000015</v>
+        <v>-0.9834736400000015</v>
       </c>
       <c r="O58">
-        <v>-0.2722499584000005</v>
+        <v>-0.3147115648000005</v>
       </c>
       <c r="P58">
-        <v>-0.5785311616000011</v>
+        <v>-0.668762075200001</v>
       </c>
       <c r="Q58">
-        <v>-7.158531161600001</v>
+        <v>-7.248762075200001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1786298465820124</v>
+        <v>0.1817189127815941</v>
       </c>
       <c r="T58">
-        <v>1.731218186652515</v>
+        <v>1.771479074714202</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.2833618654615949</v>
+        <v>0.2783906046640231</v>
       </c>
       <c r="W58">
-        <v>0.1052024781502379</v>
+        <v>0.1059322592353214</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6207,7 +6207,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8855058295674841</v>
+        <v>0.8699706395750721</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1385205202602187</v>
+        <v>0.1395305202602187</v>
       </c>
       <c r="C59">
-        <v>16.24023026823189</v>
+        <v>14.61489998721792</v>
       </c>
       <c r="D59">
-        <v>66.9505302682319</v>
+        <v>66.22909998721794</v>
       </c>
       <c r="E59">
-        <v>50.23230000000001</v>
+        <v>51.13620000000001</v>
       </c>
       <c r="F59">
-        <v>51.52230000000001</v>
+        <v>52.42620000000001</v>
       </c>
       <c r="G59">
         <v>0.8120000000000001</v>
@@ -6251,37 +6251,37 @@
         <v>6.58</v>
       </c>
       <c r="M59">
-        <v>7.563473640000002</v>
+        <v>7.696166160000002</v>
       </c>
       <c r="N59">
-        <v>-0.9834736400000015</v>
+        <v>-1.116166160000002</v>
       </c>
       <c r="O59">
-        <v>-0.3147115648000005</v>
+        <v>-0.3571731712000007</v>
       </c>
       <c r="P59">
-        <v>-0.668762075200001</v>
+        <v>-0.7589929888000015</v>
       </c>
       <c r="Q59">
-        <v>-7.248762075200001</v>
+        <v>-7.338992988800001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1817189127815941</v>
+        <v>0.1849550773716321</v>
       </c>
       <c r="T59">
-        <v>1.771479074714202</v>
+        <v>1.813657147921683</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.2783906046640231</v>
+        <v>0.2735907666525744</v>
       </c>
       <c r="W59">
-        <v>0.1059322592353214</v>
+        <v>0.1066368754554021</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8699706395750721</v>
+        <v>0.8549711457892949</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6297,22 +6297,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1395305202602187</v>
+        <v>0.1405405202602187</v>
       </c>
       <c r="C60">
-        <v>14.61489998721795</v>
+        <v>13.00495160577184</v>
       </c>
       <c r="D60">
-        <v>66.22909998721795</v>
+        <v>65.52305160577184</v>
       </c>
       <c r="E60">
-        <v>51.1362</v>
+        <v>52.0401</v>
       </c>
       <c r="F60">
-        <v>52.42619999999999</v>
+        <v>53.33009999999999</v>
       </c>
       <c r="G60">
         <v>0.8120000000000001</v>
@@ -6333,37 +6333,37 @@
         <v>6.58</v>
       </c>
       <c r="M60">
-        <v>7.69616616</v>
+        <v>7.82885868</v>
       </c>
       <c r="N60">
-        <v>-1.11616616</v>
+        <v>-1.24885868</v>
       </c>
       <c r="O60">
-        <v>-0.3571731711999999</v>
+        <v>-0.3996347775999999</v>
       </c>
       <c r="P60">
-        <v>-0.7589929887999998</v>
+        <v>-0.8492239023999998</v>
       </c>
       <c r="Q60">
-        <v>-7.338992988799999</v>
+        <v>-7.4292239024</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.184955077371632</v>
+        <v>0.1883491036489889</v>
       </c>
       <c r="T60">
-        <v>1.813657147921682</v>
+        <v>1.857892688114893</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.2735907666525745</v>
+        <v>0.2689536350143952</v>
       </c>
       <c r="W60">
-        <v>0.1066368754554021</v>
+        <v>0.1073176063798868</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8549711457892952</v>
+        <v>0.8404801094199852</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6379,22 +6379,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1405405202602187</v>
+        <v>0.1415505202602187</v>
       </c>
       <c r="C61">
-        <v>13.00495160577184</v>
+        <v>11.4098983677322</v>
       </c>
       <c r="D61">
-        <v>65.52305160577184</v>
+        <v>64.83189836773221</v>
       </c>
       <c r="E61">
-        <v>52.0401</v>
+        <v>52.944</v>
       </c>
       <c r="F61">
-        <v>53.33009999999999</v>
+        <v>54.234</v>
       </c>
       <c r="G61">
         <v>0.8120000000000001</v>
@@ -6415,37 +6415,37 @@
         <v>6.58</v>
       </c>
       <c r="M61">
-        <v>7.82885868</v>
+        <v>7.961551200000001</v>
       </c>
       <c r="N61">
-        <v>-1.24885868</v>
+        <v>-1.381551200000001</v>
       </c>
       <c r="O61">
-        <v>-0.3996347775999999</v>
+        <v>-0.4420963840000002</v>
       </c>
       <c r="P61">
-        <v>-0.8492239023999998</v>
+        <v>-0.9394548160000004</v>
       </c>
       <c r="Q61">
-        <v>-7.4292239024</v>
+        <v>-7.519454816000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1883491036489889</v>
+        <v>0.1919128312402137</v>
       </c>
       <c r="T61">
-        <v>1.857892688114893</v>
+        <v>1.904340005317766</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.2689536350143952</v>
+        <v>0.264471074430822</v>
       </c>
       <c r="W61">
-        <v>0.1073176063798868</v>
+        <v>0.1079756462735553</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8404801094199852</v>
+        <v>0.8264721075963186</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6461,22 +6461,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1415505202602187</v>
+        <v>0.1425605202602187</v>
       </c>
       <c r="C62">
-        <v>11.4098983677322</v>
+        <v>9.829273840256377</v>
       </c>
       <c r="D62">
-        <v>64.83189836773221</v>
+        <v>64.15517384025638</v>
       </c>
       <c r="E62">
-        <v>52.944</v>
+        <v>53.8479</v>
       </c>
       <c r="F62">
-        <v>54.234</v>
+        <v>55.1379</v>
       </c>
       <c r="G62">
         <v>0.8120000000000001</v>
@@ -6497,37 +6497,37 @@
         <v>6.58</v>
       </c>
       <c r="M62">
-        <v>7.961551200000001</v>
+        <v>8.094243720000001</v>
       </c>
       <c r="N62">
-        <v>-1.381551200000001</v>
+        <v>-1.514243720000001</v>
       </c>
       <c r="O62">
-        <v>-0.4420963840000002</v>
+        <v>-0.4845579904000005</v>
       </c>
       <c r="P62">
-        <v>-0.9394548160000004</v>
+        <v>-1.029685729600001</v>
       </c>
       <c r="Q62">
-        <v>-7.519454816000001</v>
+        <v>-7.609685729600001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1919128312402137</v>
+        <v>0.1956593140925268</v>
       </c>
       <c r="T62">
-        <v>1.904340005317766</v>
+        <v>1.95316923622335</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.264471074430822</v>
+        <v>0.2601354830467101</v>
       </c>
       <c r="W62">
-        <v>0.1079756462735553</v>
+        <v>0.108612111088743</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6535,7 +6535,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8264721075963186</v>
+        <v>0.812923384520969</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6543,22 +6543,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1425605202602187</v>
+        <v>0.1800149965480014</v>
       </c>
       <c r="C63">
-        <v>9.829273840256377</v>
+        <v>-8.977978982757513</v>
       </c>
       <c r="D63">
-        <v>64.15517384025638</v>
+        <v>46.25182101724249</v>
       </c>
       <c r="E63">
-        <v>53.8479</v>
+        <v>54.7518</v>
       </c>
       <c r="F63">
-        <v>55.1379</v>
+        <v>56.0418</v>
       </c>
       <c r="G63">
         <v>0.8120000000000001</v>
@@ -6579,45 +6579,45 @@
         <v>6.58</v>
       </c>
       <c r="M63">
-        <v>8.094243720000001</v>
+        <v>11.25319344</v>
       </c>
       <c r="N63">
-        <v>-1.514243720000001</v>
+        <v>-4.67319344</v>
       </c>
       <c r="O63">
-        <v>-0.4845579904000005</v>
+        <v>-1.4954219008</v>
       </c>
       <c r="P63">
-        <v>-1.029685729600001</v>
+        <v>-3.1777715392</v>
       </c>
       <c r="Q63">
-        <v>-7.609685729600001</v>
+        <v>-9.7577715392</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1956593140925268</v>
+        <v>0.2074042336417584</v>
       </c>
       <c r="T63">
-        <v>1.95316923622335</v>
+        <v>2.106244910460814</v>
       </c>
       <c r="U63">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.2601354830467101</v>
+        <v>0.1871113307726096</v>
       </c>
       <c r="W63">
-        <v>0.108612111088743</v>
+        <v>0.16322804478086</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y63">
-        <v>0.812923384520969</v>
+        <v>0.5847229086644048</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6625,22 +6625,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1800149965480014</v>
+        <v>0.1815649965480014</v>
       </c>
       <c r="C64">
-        <v>-8.977978982757513</v>
+        <v>-10.40992615544225</v>
       </c>
       <c r="D64">
-        <v>46.25182101724249</v>
+        <v>45.72377384455775</v>
       </c>
       <c r="E64">
-        <v>54.7518</v>
+        <v>55.6557</v>
       </c>
       <c r="F64">
-        <v>56.0418</v>
+        <v>56.9457</v>
       </c>
       <c r="G64">
         <v>0.8120000000000001</v>
@@ -6661,37 +6661,37 @@
         <v>6.58</v>
       </c>
       <c r="M64">
-        <v>11.25319344</v>
+        <v>11.43469656</v>
       </c>
       <c r="N64">
-        <v>-4.67319344</v>
+        <v>-4.854696560000001</v>
       </c>
       <c r="O64">
-        <v>-1.4954219008</v>
+        <v>-1.5535028992</v>
       </c>
       <c r="P64">
-        <v>-3.1777715392</v>
+        <v>-3.301193660800001</v>
       </c>
       <c r="Q64">
-        <v>-9.7577715392</v>
+        <v>-9.881193660800001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2074042336417584</v>
+        <v>0.2117719156320762</v>
       </c>
       <c r="T64">
-        <v>2.106244910460814</v>
+        <v>2.163170448581376</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1871113307726096</v>
+        <v>0.1841413096492348</v>
       </c>
       <c r="W64">
-        <v>0.16322804478086</v>
+        <v>0.1638244250224337</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5847229086644048</v>
+        <v>0.5754415926538587</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6707,22 +6707,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1815649965480014</v>
+        <v>0.1831149965480014</v>
       </c>
       <c r="C65">
-        <v>-10.40992615544225</v>
+        <v>-11.82995222499571</v>
       </c>
       <c r="D65">
-        <v>45.72377384455775</v>
+        <v>45.2076477750043</v>
       </c>
       <c r="E65">
-        <v>55.6557</v>
+        <v>56.5596</v>
       </c>
       <c r="F65">
-        <v>56.9457</v>
+        <v>57.8496</v>
       </c>
       <c r="G65">
         <v>0.8120000000000001</v>
@@ -6743,37 +6743,37 @@
         <v>6.58</v>
       </c>
       <c r="M65">
-        <v>11.43469656</v>
+        <v>11.61619968</v>
       </c>
       <c r="N65">
-        <v>-4.854696560000001</v>
+        <v>-5.036199680000001</v>
       </c>
       <c r="O65">
-        <v>-1.5535028992</v>
+        <v>-1.6115838976</v>
       </c>
       <c r="P65">
-        <v>-3.301193660800001</v>
+        <v>-3.424615782400001</v>
       </c>
       <c r="Q65">
-        <v>-9.881193660800001</v>
+        <v>-10.0046157824</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2117719156320762</v>
+        <v>0.2163822466218562</v>
       </c>
       <c r="T65">
-        <v>2.163170448581376</v>
+        <v>2.223258516597526</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1841413096492348</v>
+        <v>0.1812641016859655</v>
       </c>
       <c r="W65">
-        <v>0.1638244250224337</v>
+        <v>0.1644021683814581</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6781,7 +6781,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5754415926538587</v>
+        <v>0.5664503177686422</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6789,22 +6789,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1831149965480014</v>
+        <v>0.1846649965480014</v>
       </c>
       <c r="C66">
-        <v>-11.82995222499571</v>
+        <v>-13.23845637862081</v>
       </c>
       <c r="D66">
-        <v>45.2076477750043</v>
+        <v>44.70304362137919</v>
       </c>
       <c r="E66">
-        <v>56.5596</v>
+        <v>57.4635</v>
       </c>
       <c r="F66">
-        <v>57.8496</v>
+        <v>58.7535</v>
       </c>
       <c r="G66">
         <v>0.8120000000000001</v>
@@ -6825,37 +6825,37 @@
         <v>6.58</v>
       </c>
       <c r="M66">
-        <v>11.61619968</v>
+        <v>11.7977028</v>
       </c>
       <c r="N66">
-        <v>-5.036199680000001</v>
+        <v>-5.217702800000001</v>
       </c>
       <c r="O66">
-        <v>-1.6115838976</v>
+        <v>-1.669664896</v>
       </c>
       <c r="P66">
-        <v>-3.424615782400001</v>
+        <v>-3.548037904000001</v>
       </c>
       <c r="Q66">
-        <v>-10.0046157824</v>
+        <v>-10.128037904</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2163822466218562</v>
+        <v>0.2212560250967664</v>
       </c>
       <c r="T66">
-        <v>2.223258516597526</v>
+        <v>2.286780188500313</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1812641016859655</v>
+        <v>0.1784754231984891</v>
       </c>
       <c r="W66">
-        <v>0.1644021683814581</v>
+        <v>0.1649621350217434</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6863,7 +6863,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5664503177686422</v>
+        <v>0.5577356974952784</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6871,22 +6871,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1846649965480014</v>
+        <v>0.1862149965480014</v>
       </c>
       <c r="C67">
-        <v>-13.23845637862081</v>
+        <v>-14.63582017747828</v>
       </c>
       <c r="D67">
-        <v>44.70304362137919</v>
+        <v>44.20957982252173</v>
       </c>
       <c r="E67">
-        <v>57.4635</v>
+        <v>58.3674</v>
       </c>
       <c r="F67">
-        <v>58.7535</v>
+        <v>59.6574</v>
       </c>
       <c r="G67">
         <v>0.8120000000000001</v>
@@ -6907,37 +6907,37 @@
         <v>6.58</v>
       </c>
       <c r="M67">
-        <v>11.7977028</v>
+        <v>11.97920592</v>
       </c>
       <c r="N67">
-        <v>-5.217702800000001</v>
+        <v>-5.39920592</v>
       </c>
       <c r="O67">
-        <v>-1.669664896</v>
+        <v>-1.7277458944</v>
       </c>
       <c r="P67">
-        <v>-3.548037904000001</v>
+        <v>-3.6714600256</v>
       </c>
       <c r="Q67">
-        <v>-10.128037904</v>
+        <v>-10.2514600256</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2212560250967664</v>
+        <v>0.2264164964231418</v>
       </c>
       <c r="T67">
-        <v>2.286780188500313</v>
+        <v>2.354038429338556</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1784754231984891</v>
+        <v>0.1757712501197241</v>
       </c>
       <c r="W67">
-        <v>0.1649621350217434</v>
+        <v>0.1655051329759594</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5577356974952784</v>
+        <v>0.5492851566241379</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6953,22 +6953,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1862149965480014</v>
+        <v>0.1877649965480014</v>
       </c>
       <c r="C68">
-        <v>-14.63582017747828</v>
+        <v>-16.02240851890856</v>
       </c>
       <c r="D68">
-        <v>44.20957982252173</v>
+        <v>43.72689148109145</v>
       </c>
       <c r="E68">
-        <v>58.3674</v>
+        <v>59.2713</v>
       </c>
       <c r="F68">
-        <v>59.6574</v>
+        <v>60.5613</v>
       </c>
       <c r="G68">
         <v>0.8120000000000001</v>
@@ -6989,37 +6989,37 @@
         <v>6.58</v>
       </c>
       <c r="M68">
-        <v>11.97920592</v>
+        <v>12.16070904</v>
       </c>
       <c r="N68">
-        <v>-5.39920592</v>
+        <v>-5.58070904</v>
       </c>
       <c r="O68">
-        <v>-1.7277458944</v>
+        <v>-1.7858268928</v>
       </c>
       <c r="P68">
-        <v>-3.6714600256</v>
+        <v>-3.7948821472</v>
       </c>
       <c r="Q68">
-        <v>-10.2514600256</v>
+        <v>-10.3748821472</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2264164964231418</v>
+        <v>0.2318897235874794</v>
       </c>
       <c r="T68">
-        <v>2.354038429338556</v>
+        <v>2.425372927197301</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1757712501197241</v>
+        <v>0.1731477986253999</v>
       </c>
       <c r="W68">
-        <v>0.1655051329759594</v>
+        <v>0.1660319220360197</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5492851566241379</v>
+        <v>0.5410868707043747</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7035,22 +7035,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1877649965480014</v>
+        <v>0.1893149965480014</v>
       </c>
       <c r="C69">
-        <v>-16.02240851890856</v>
+        <v>-17.39857053630005</v>
       </c>
       <c r="D69">
-        <v>43.72689148109145</v>
+        <v>43.25462946369996</v>
       </c>
       <c r="E69">
-        <v>59.2713</v>
+        <v>60.1752</v>
       </c>
       <c r="F69">
-        <v>60.5613</v>
+        <v>61.4652</v>
       </c>
       <c r="G69">
         <v>0.8120000000000001</v>
@@ -7071,37 +7071,37 @@
         <v>6.58</v>
       </c>
       <c r="M69">
-        <v>12.16070904</v>
+        <v>12.34221216</v>
       </c>
       <c r="N69">
-        <v>-5.58070904</v>
+        <v>-5.762212160000001</v>
       </c>
       <c r="O69">
-        <v>-1.7858268928</v>
+        <v>-1.8439078912</v>
       </c>
       <c r="P69">
-        <v>-3.7948821472</v>
+        <v>-3.9183042688</v>
       </c>
       <c r="Q69">
-        <v>-10.3748821472</v>
+        <v>-10.4983042688</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2318897235874794</v>
+        <v>0.2377050274495882</v>
       </c>
       <c r="T69">
-        <v>2.425372927197301</v>
+        <v>2.501165831172216</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1731477986253999</v>
+        <v>0.170601507469144</v>
       </c>
       <c r="W69">
-        <v>0.1660319220360197</v>
+        <v>0.1665432173001959</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7109,7 +7109,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5410868707043747</v>
+        <v>0.5331297108410751</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7117,22 +7117,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1893149965480014</v>
+        <v>0.1908649965480014</v>
       </c>
       <c r="C70">
-        <v>-17.39857053630005</v>
+        <v>-18.76464044126779</v>
       </c>
       <c r="D70">
-        <v>43.25462946369996</v>
+        <v>42.79245955873222</v>
       </c>
       <c r="E70">
-        <v>60.1752</v>
+        <v>61.0791</v>
       </c>
       <c r="F70">
-        <v>61.4652</v>
+        <v>62.3691</v>
       </c>
       <c r="G70">
         <v>0.8120000000000001</v>
@@ -7153,37 +7153,37 @@
         <v>6.58</v>
       </c>
       <c r="M70">
-        <v>12.34221216</v>
+        <v>12.52371528</v>
       </c>
       <c r="N70">
-        <v>-5.762212160000001</v>
+        <v>-5.943715280000001</v>
       </c>
       <c r="O70">
-        <v>-1.8439078912</v>
+        <v>-1.9019888896</v>
       </c>
       <c r="P70">
-        <v>-3.9183042688</v>
+        <v>-4.041726390400001</v>
       </c>
       <c r="Q70">
-        <v>-10.4983042688</v>
+        <v>-10.6217263904</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2377050274495882</v>
+        <v>0.2438955122060265</v>
       </c>
       <c r="T70">
-        <v>2.501165831172216</v>
+        <v>2.581848599919708</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.170601507469144</v>
+        <v>0.1681290218536492</v>
       </c>
       <c r="W70">
-        <v>0.1665432173001959</v>
+        <v>0.1670396924117872</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5331297108410751</v>
+        <v>0.5254031932926536</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7199,22 +7199,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1908649965480014</v>
+        <v>0.1924149965480014</v>
       </c>
       <c r="C71">
-        <v>-18.76464044126779</v>
+        <v>-20.12093831241134</v>
       </c>
       <c r="D71">
-        <v>42.79245955873222</v>
+        <v>42.34006168758867</v>
       </c>
       <c r="E71">
-        <v>61.0791</v>
+        <v>61.983</v>
       </c>
       <c r="F71">
-        <v>62.3691</v>
+        <v>63.273</v>
       </c>
       <c r="G71">
         <v>0.8120000000000001</v>
@@ -7235,37 +7235,37 @@
         <v>6.58</v>
       </c>
       <c r="M71">
-        <v>12.52371528</v>
+        <v>12.7052184</v>
       </c>
       <c r="N71">
-        <v>-5.943715280000001</v>
+        <v>-6.125218400000001</v>
       </c>
       <c r="O71">
-        <v>-1.9019888896</v>
+        <v>-1.960069888</v>
       </c>
       <c r="P71">
-        <v>-4.041726390400001</v>
+        <v>-4.165148512000001</v>
       </c>
       <c r="Q71">
-        <v>-10.6217263904</v>
+        <v>-10.745148512</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2438955122060265</v>
+        <v>0.2504986959462274</v>
       </c>
       <c r="T71">
-        <v>2.581848599919708</v>
+        <v>2.667910219917031</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1681290218536492</v>
+        <v>0.1657271786843113</v>
       </c>
       <c r="W71">
-        <v>0.1670396924117872</v>
+        <v>0.1675219825201903</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5254031932926536</v>
+        <v>0.5178974333884728</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7281,22 +7281,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1924149965480014</v>
+        <v>0.1939649965480014</v>
       </c>
       <c r="C72">
-        <v>-20.12093831241134</v>
+        <v>-21.46777083456411</v>
       </c>
       <c r="D72">
-        <v>42.34006168758867</v>
+        <v>41.8971291654359</v>
       </c>
       <c r="E72">
-        <v>61.983</v>
+        <v>62.8869</v>
       </c>
       <c r="F72">
-        <v>63.273</v>
+        <v>64.1769</v>
       </c>
       <c r="G72">
         <v>0.8120000000000001</v>
@@ -7317,37 +7317,37 @@
         <v>6.58</v>
       </c>
       <c r="M72">
-        <v>12.7052184</v>
+        <v>12.88672152</v>
       </c>
       <c r="N72">
-        <v>-6.125218400000001</v>
+        <v>-6.306721520000002</v>
       </c>
       <c r="O72">
-        <v>-1.960069888</v>
+        <v>-2.0181508864</v>
       </c>
       <c r="P72">
-        <v>-4.165148512000001</v>
+        <v>-4.288570633600001</v>
       </c>
       <c r="Q72">
-        <v>-10.745148512</v>
+        <v>-10.8685706336</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2504986959462274</v>
+        <v>0.2575572716685111</v>
       </c>
       <c r="T72">
-        <v>2.667910219917031</v>
+        <v>2.759907124052102</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1657271786843113</v>
+        <v>0.1633929930690393</v>
       </c>
       <c r="W72">
-        <v>0.1675219825201903</v>
+        <v>0.1679906869917369</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5178974333884728</v>
+        <v>0.5106031033407479</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7363,22 +7363,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1939649965480014</v>
+        <v>0.1955149965480014</v>
       </c>
       <c r="C73">
-        <v>-21.46777083456411</v>
+        <v>-22.80543199212191</v>
       </c>
       <c r="D73">
-        <v>41.8971291654359</v>
+        <v>41.46336800787809</v>
       </c>
       <c r="E73">
-        <v>62.8869</v>
+        <v>63.7908</v>
       </c>
       <c r="F73">
-        <v>64.1769</v>
+        <v>65.0808</v>
       </c>
       <c r="G73">
         <v>0.8120000000000001</v>
@@ -7399,37 +7399,37 @@
         <v>6.58</v>
       </c>
       <c r="M73">
-        <v>12.88672152</v>
+        <v>13.06822464</v>
       </c>
       <c r="N73">
-        <v>-6.306721520000002</v>
+        <v>-6.48822464</v>
       </c>
       <c r="O73">
-        <v>-2.0181508864</v>
+        <v>-2.0762318848</v>
       </c>
       <c r="P73">
-        <v>-4.288570633600001</v>
+        <v>-4.4119927552</v>
       </c>
       <c r="Q73">
-        <v>-10.8685706336</v>
+        <v>-10.9919927552</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.257557271668511</v>
+        <v>0.2651200313709579</v>
       </c>
       <c r="T73">
-        <v>2.7599071240521</v>
+        <v>2.85847523562539</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1633929930690393</v>
+        <v>0.1611236459430805</v>
       </c>
       <c r="W73">
-        <v>0.1679906869917369</v>
+        <v>0.1684463718946294</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5106031033407479</v>
+        <v>0.5035113935721264</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7445,22 +7445,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1955149965480014</v>
+        <v>0.2238111985370244</v>
       </c>
       <c r="C74">
-        <v>-22.80543199212191</v>
+        <v>-30.30024226034354</v>
       </c>
       <c r="D74">
-        <v>41.46336800787809</v>
+        <v>34.87245773965646</v>
       </c>
       <c r="E74">
-        <v>63.7908</v>
+        <v>64.6947</v>
       </c>
       <c r="F74">
-        <v>65.0808</v>
+        <v>65.9847</v>
       </c>
       <c r="G74">
         <v>0.8120000000000001</v>
@@ -7481,45 +7481,45 @@
         <v>6.58</v>
       </c>
       <c r="M74">
-        <v>13.06822464</v>
+        <v>15.55919226</v>
       </c>
       <c r="N74">
-        <v>-6.48822464</v>
+        <v>-8.979192260000001</v>
       </c>
       <c r="O74">
-        <v>-2.0762318848</v>
+        <v>-2.873341523200001</v>
       </c>
       <c r="P74">
-        <v>-4.4119927552</v>
+        <v>-6.105850736800001</v>
       </c>
       <c r="Q74">
-        <v>-10.9919927552</v>
+        <v>-12.6858507368</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2651200313709579</v>
+        <v>0.2776733732329304</v>
       </c>
       <c r="T74">
-        <v>2.85847523562539</v>
+        <v>3.022087362673168</v>
       </c>
       <c r="U74">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.1611236459430805</v>
+        <v>0.135328361833611</v>
       </c>
       <c r="W74">
-        <v>0.1684463718946294</v>
+        <v>0.2038895722796345</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y74">
-        <v>0.5035113935721264</v>
+        <v>0.4229011307300344</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7527,22 +7527,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2238111985370244</v>
+        <v>0.2257111985370244</v>
       </c>
       <c r="C75">
-        <v>-30.30024226034354</v>
+        <v>-31.57242211309385</v>
       </c>
       <c r="D75">
-        <v>34.87245773965646</v>
+        <v>34.50417788690615</v>
       </c>
       <c r="E75">
-        <v>64.6947</v>
+        <v>65.59859999999999</v>
       </c>
       <c r="F75">
-        <v>65.9847</v>
+        <v>66.8886</v>
       </c>
       <c r="G75">
         <v>0.8120000000000001</v>
@@ -7563,37 +7563,37 @@
         <v>6.58</v>
       </c>
       <c r="M75">
-        <v>15.55919226</v>
+        <v>15.77233188</v>
       </c>
       <c r="N75">
-        <v>-8.979192260000001</v>
+        <v>-9.192331879999999</v>
       </c>
       <c r="O75">
-        <v>-2.873341523200001</v>
+        <v>-2.9415462016</v>
       </c>
       <c r="P75">
-        <v>-6.105850736800001</v>
+        <v>-6.2507856784</v>
       </c>
       <c r="Q75">
-        <v>-12.6858507368</v>
+        <v>-12.8307856784</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2776733732329304</v>
+        <v>0.2865915798957354</v>
       </c>
       <c r="T75">
-        <v>3.022087362673168</v>
+        <v>3.138321492006752</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.135328361833611</v>
+        <v>0.1334996001872109</v>
       </c>
       <c r="W75">
-        <v>0.2038895722796345</v>
+        <v>0.2043207942758557</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.4229011307300344</v>
+        <v>0.417186250585034</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7609,22 +7609,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2257111985370244</v>
+        <v>0.2276111985370244</v>
       </c>
       <c r="C76">
-        <v>-31.57242211309385</v>
+        <v>-32.83690462128171</v>
       </c>
       <c r="D76">
-        <v>34.50417788690615</v>
+        <v>34.1435953787183</v>
       </c>
       <c r="E76">
-        <v>65.59859999999999</v>
+        <v>66.5025</v>
       </c>
       <c r="F76">
-        <v>66.8886</v>
+        <v>67.7925</v>
       </c>
       <c r="G76">
         <v>0.8120000000000001</v>
@@ -7645,37 +7645,37 @@
         <v>6.58</v>
       </c>
       <c r="M76">
-        <v>15.77233188</v>
+        <v>15.9854715</v>
       </c>
       <c r="N76">
-        <v>-9.192331879999999</v>
+        <v>-9.405471500000001</v>
       </c>
       <c r="O76">
-        <v>-2.9415462016</v>
+        <v>-3.00975088</v>
       </c>
       <c r="P76">
-        <v>-6.2507856784</v>
+        <v>-6.395720620000001</v>
       </c>
       <c r="Q76">
-        <v>-12.8307856784</v>
+        <v>-12.97572062</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2865915798957354</v>
+        <v>0.2962232430915648</v>
       </c>
       <c r="T76">
-        <v>3.138321492006752</v>
+        <v>3.263854351687022</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.1334996001872109</v>
+        <v>0.131719605518048</v>
       </c>
       <c r="W76">
-        <v>0.2043207942758557</v>
+        <v>0.2047405170188443</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.417186250585034</v>
+        <v>0.4116237672439002</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7691,22 +7691,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2276111985370244</v>
+        <v>0.2295111985370244</v>
       </c>
       <c r="C77">
-        <v>-32.83690462128171</v>
+        <v>-34.09392861010861</v>
       </c>
       <c r="D77">
-        <v>34.1435953787183</v>
+        <v>33.79047138989139</v>
       </c>
       <c r="E77">
-        <v>66.5025</v>
+        <v>67.40639999999999</v>
       </c>
       <c r="F77">
-        <v>67.7925</v>
+        <v>68.6964</v>
       </c>
       <c r="G77">
         <v>0.8120000000000001</v>
@@ -7727,37 +7727,37 @@
         <v>6.58</v>
       </c>
       <c r="M77">
-        <v>15.9854715</v>
+        <v>16.19861112</v>
       </c>
       <c r="N77">
-        <v>-9.405471500000001</v>
+        <v>-9.618611119999999</v>
       </c>
       <c r="O77">
-        <v>-3.00975088</v>
+        <v>-3.0779555584</v>
       </c>
       <c r="P77">
-        <v>-6.395720620000001</v>
+        <v>-6.5406555616</v>
       </c>
       <c r="Q77">
-        <v>-12.97572062</v>
+        <v>-13.1206555616</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2962232430915648</v>
+        <v>0.3066575448870467</v>
       </c>
       <c r="T77">
-        <v>3.263854351687022</v>
+        <v>3.399848283007314</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.131719605518048</v>
+        <v>0.1299864528138632</v>
       </c>
       <c r="W77">
-        <v>0.2047405170188443</v>
+        <v>0.2051491944264911</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.4116237672439002</v>
+        <v>0.4062076650433226</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7773,22 +7773,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2295111985370244</v>
+        <v>0.2314111985370244</v>
       </c>
       <c r="C78">
-        <v>-34.09392861010861</v>
+        <v>-35.34372312588584</v>
       </c>
       <c r="D78">
-        <v>33.79047138989139</v>
+        <v>33.44457687411417</v>
       </c>
       <c r="E78">
-        <v>67.40639999999999</v>
+        <v>68.3103</v>
       </c>
       <c r="F78">
-        <v>68.6964</v>
+        <v>69.6003</v>
       </c>
       <c r="G78">
         <v>0.8120000000000001</v>
@@ -7809,37 +7809,37 @@
         <v>6.58</v>
       </c>
       <c r="M78">
-        <v>16.19861112</v>
+        <v>16.41175074</v>
       </c>
       <c r="N78">
-        <v>-9.618611119999999</v>
+        <v>-9.831750740000002</v>
       </c>
       <c r="O78">
-        <v>-3.0779555584</v>
+        <v>-3.146160236800001</v>
       </c>
       <c r="P78">
-        <v>-6.5406555616</v>
+        <v>-6.685590503200002</v>
       </c>
       <c r="Q78">
-        <v>-13.1206555616</v>
+        <v>-13.2655905032</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3066575448870467</v>
+        <v>0.3179991772734401</v>
       </c>
       <c r="T78">
-        <v>3.399848283007314</v>
+        <v>3.54766777357285</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.1299864528138632</v>
+        <v>0.1282983170630338</v>
       </c>
       <c r="W78">
-        <v>0.2051491944264911</v>
+        <v>0.2055472568365366</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7847,7 +7847,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4062076650433226</v>
+        <v>0.4009322408219806</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7855,22 +7855,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2314111985370244</v>
+        <v>0.2333111985370244</v>
       </c>
       <c r="C79">
-        <v>-35.34372312588584</v>
+        <v>-36.58650793146863</v>
       </c>
       <c r="D79">
-        <v>33.44457687411417</v>
+        <v>33.10569206853137</v>
       </c>
       <c r="E79">
-        <v>68.3103</v>
+        <v>69.21419999999999</v>
       </c>
       <c r="F79">
-        <v>69.6003</v>
+        <v>70.5042</v>
       </c>
       <c r="G79">
         <v>0.8120000000000001</v>
@@ -7891,37 +7891,37 @@
         <v>6.58</v>
       </c>
       <c r="M79">
-        <v>16.41175074</v>
+        <v>16.62489036</v>
       </c>
       <c r="N79">
-        <v>-9.831750740000002</v>
+        <v>-10.04489036</v>
       </c>
       <c r="O79">
-        <v>-3.146160236800001</v>
+        <v>-3.2143649152</v>
       </c>
       <c r="P79">
-        <v>-6.685590503200002</v>
+        <v>-6.830525444799999</v>
       </c>
       <c r="Q79">
-        <v>-13.2655905032</v>
+        <v>-13.4105254448</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3179991772734401</v>
+        <v>0.3303718671495055</v>
       </c>
       <c r="T79">
-        <v>3.54766777357285</v>
+        <v>3.708925399644344</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.1282983170630338</v>
+        <v>0.126653466844277</v>
       </c>
       <c r="W79">
-        <v>0.2055472568365366</v>
+        <v>0.2059351125181195</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4009322408219806</v>
+        <v>0.3957920838883656</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7937,22 +7937,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2333111985370244</v>
+        <v>0.2352111985370244</v>
       </c>
       <c r="C80">
-        <v>-36.58650793146863</v>
+        <v>-37.82249397187198</v>
       </c>
       <c r="D80">
-        <v>33.10569206853137</v>
+        <v>32.77360602812803</v>
       </c>
       <c r="E80">
-        <v>69.21419999999999</v>
+        <v>70.1181</v>
       </c>
       <c r="F80">
-        <v>70.5042</v>
+        <v>71.4081</v>
       </c>
       <c r="G80">
         <v>0.8120000000000001</v>
@@ -7973,37 +7973,37 @@
         <v>6.58</v>
       </c>
       <c r="M80">
-        <v>16.62489036</v>
+        <v>16.83802998</v>
       </c>
       <c r="N80">
-        <v>-10.04489036</v>
+        <v>-10.25802998</v>
       </c>
       <c r="O80">
-        <v>-3.2143649152</v>
+        <v>-3.282569593600001</v>
       </c>
       <c r="P80">
-        <v>-6.830525444799999</v>
+        <v>-6.975460386400001</v>
       </c>
       <c r="Q80">
-        <v>-13.4105254448</v>
+        <v>-13.5554603864</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3303718671495055</v>
+        <v>0.3439229084423392</v>
       </c>
       <c r="T80">
-        <v>3.708925399644344</v>
+        <v>3.885540894865504</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.126653466844277</v>
+        <v>0.1250502584032102</v>
       </c>
       <c r="W80">
-        <v>0.2059351125181195</v>
+        <v>0.206313149068523</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3957920838883656</v>
+        <v>0.3907820575100318</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8019,22 +8019,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2352111985370244</v>
+        <v>0.2371111985370244</v>
       </c>
       <c r="C81">
-        <v>-37.82249397187198</v>
+        <v>-39.05188381214073</v>
       </c>
       <c r="D81">
-        <v>32.77360602812803</v>
+        <v>32.44811618785927</v>
       </c>
       <c r="E81">
-        <v>70.1181</v>
+        <v>71.02199999999999</v>
       </c>
       <c r="F81">
-        <v>71.4081</v>
+        <v>72.312</v>
       </c>
       <c r="G81">
         <v>0.8120000000000001</v>
@@ -8055,37 +8055,37 @@
         <v>6.58</v>
       </c>
       <c r="M81">
-        <v>16.83802998</v>
+        <v>17.0511696</v>
       </c>
       <c r="N81">
-        <v>-10.25802998</v>
+        <v>-10.4711696</v>
       </c>
       <c r="O81">
-        <v>-3.282569593600001</v>
+        <v>-3.350774272000001</v>
       </c>
       <c r="P81">
-        <v>-6.975460386400001</v>
+        <v>-7.120395328000001</v>
       </c>
       <c r="Q81">
-        <v>-13.5554603864</v>
+        <v>-13.700395328</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3439229084423392</v>
+        <v>0.3588290538644561</v>
       </c>
       <c r="T81">
-        <v>3.885540894865504</v>
+        <v>4.079817939608778</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.1250502584032102</v>
+        <v>0.12348713017317</v>
       </c>
       <c r="W81">
-        <v>0.206313149068523</v>
+        <v>0.2066817347051665</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3907820575100318</v>
+        <v>0.3858972817911563</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8101,22 +8101,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2371111985370244</v>
+        <v>0.2390111985370244</v>
       </c>
       <c r="C82">
-        <v>-39.05188381214073</v>
+        <v>-40.2748720493845</v>
       </c>
       <c r="D82">
-        <v>32.44811618785927</v>
+        <v>32.12902795061551</v>
       </c>
       <c r="E82">
-        <v>71.02199999999999</v>
+        <v>71.9259</v>
       </c>
       <c r="F82">
-        <v>72.312</v>
+        <v>73.2159</v>
       </c>
       <c r="G82">
         <v>0.8120000000000001</v>
@@ -8137,37 +8137,37 @@
         <v>6.58</v>
       </c>
       <c r="M82">
-        <v>17.0511696</v>
+        <v>17.26430922</v>
       </c>
       <c r="N82">
-        <v>-10.4711696</v>
+        <v>-10.68430922</v>
       </c>
       <c r="O82">
-        <v>-3.350774272000001</v>
+        <v>-3.418978950400001</v>
       </c>
       <c r="P82">
-        <v>-7.120395328000001</v>
+        <v>-7.265330269600001</v>
       </c>
       <c r="Q82">
-        <v>-13.700395328</v>
+        <v>-13.8453302696</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3588290538644561</v>
+        <v>0.3753042672257433</v>
       </c>
       <c r="T82">
-        <v>4.079817939608778</v>
+        <v>4.294545199588188</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.12348713017317</v>
+        <v>0.1219625977018963</v>
       </c>
       <c r="W82">
-        <v>0.2066817347051665</v>
+        <v>0.2070412194618929</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8175,7 +8175,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3858972817911563</v>
+        <v>0.3811331178184261</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8183,22 +8183,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2390111985370244</v>
+        <v>0.2409111985370244</v>
       </c>
       <c r="C83">
-        <v>-40.2748720493845</v>
+        <v>-41.49164570073766</v>
       </c>
       <c r="D83">
-        <v>32.12902795061551</v>
+        <v>31.81615429926236</v>
       </c>
       <c r="E83">
-        <v>71.9259</v>
+        <v>72.82980000000001</v>
       </c>
       <c r="F83">
-        <v>73.2159</v>
+        <v>74.11980000000001</v>
       </c>
       <c r="G83">
         <v>0.8120000000000001</v>
@@ -8219,37 +8219,37 @@
         <v>6.58</v>
       </c>
       <c r="M83">
-        <v>17.26430922</v>
+        <v>17.47744884</v>
       </c>
       <c r="N83">
-        <v>-10.68430922</v>
+        <v>-10.89744884</v>
       </c>
       <c r="O83">
-        <v>-3.418978950400001</v>
+        <v>-3.487183628800001</v>
       </c>
       <c r="P83">
-        <v>-7.265330269600001</v>
+        <v>-7.410265211200003</v>
       </c>
       <c r="Q83">
-        <v>-13.8453302696</v>
+        <v>-13.9902652112</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3753042672257433</v>
+        <v>0.3936100598493957</v>
       </c>
       <c r="T83">
-        <v>4.294545199588188</v>
+        <v>4.533131044009754</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.1219625977018963</v>
+        <v>0.1204752489494342</v>
       </c>
       <c r="W83">
-        <v>0.2070412194618929</v>
+        <v>0.2073919362977234</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8257,7 +8257,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3811331178184261</v>
+        <v>0.3764851529669818</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8265,22 +8265,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2409111985370244</v>
+        <v>0.2428111985370244</v>
       </c>
       <c r="C84">
-        <v>-41.49164570073766</v>
+        <v>-42.70238456887051</v>
       </c>
       <c r="D84">
-        <v>31.81615429926236</v>
+        <v>31.5093154311295</v>
       </c>
       <c r="E84">
-        <v>72.82980000000001</v>
+        <v>73.7337</v>
       </c>
       <c r="F84">
-        <v>74.11980000000001</v>
+        <v>75.02370000000001</v>
       </c>
       <c r="G84">
         <v>0.8120000000000001</v>
@@ -8301,37 +8301,37 @@
         <v>6.58</v>
       </c>
       <c r="M84">
-        <v>17.47744884</v>
+        <v>17.69058846</v>
       </c>
       <c r="N84">
-        <v>-10.89744884</v>
+        <v>-11.11058846</v>
       </c>
       <c r="O84">
-        <v>-3.487183628800001</v>
+        <v>-3.5553883072</v>
       </c>
       <c r="P84">
-        <v>-7.410265211200003</v>
+        <v>-7.5552001528</v>
       </c>
       <c r="Q84">
-        <v>-13.9902652112</v>
+        <v>-14.1352001528</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3936100598493957</v>
+        <v>0.4140694751346543</v>
       </c>
       <c r="T84">
-        <v>4.533131044009754</v>
+        <v>4.799785811304446</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.1204752489494342</v>
+        <v>0.119023739925947</v>
       </c>
       <c r="W84">
-        <v>0.2073919362977234</v>
+        <v>0.2077342021254617</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8339,7 +8339,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3764851529669818</v>
+        <v>0.3719491872685845</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8347,22 +8347,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2428111985370244</v>
+        <v>0.2447111985370244</v>
       </c>
       <c r="C85">
-        <v>-42.70238456887051</v>
+        <v>-43.90726158655212</v>
       </c>
       <c r="D85">
-        <v>31.5093154311295</v>
+        <v>31.2083384134479</v>
       </c>
       <c r="E85">
-        <v>73.7337</v>
+        <v>74.63760000000001</v>
       </c>
       <c r="F85">
-        <v>75.02370000000001</v>
+        <v>75.92760000000001</v>
       </c>
       <c r="G85">
         <v>0.8120000000000001</v>
@@ -8383,37 +8383,37 @@
         <v>6.58</v>
       </c>
       <c r="M85">
-        <v>17.69058846</v>
+        <v>17.90372808</v>
       </c>
       <c r="N85">
-        <v>-11.11058846</v>
+        <v>-11.32372808</v>
       </c>
       <c r="O85">
-        <v>-3.5553883072</v>
+        <v>-3.623592985600002</v>
       </c>
       <c r="P85">
-        <v>-7.5552001528</v>
+        <v>-7.700135094400002</v>
       </c>
       <c r="Q85">
-        <v>-14.1352001528</v>
+        <v>-14.2801350944</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4140694751346543</v>
+        <v>0.4370863173305702</v>
       </c>
       <c r="T85">
-        <v>4.799785811304446</v>
+        <v>5.099772424510975</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.119023739925947</v>
+        <v>0.1176067906411143</v>
       </c>
       <c r="W85">
-        <v>0.2077342021254617</v>
+        <v>0.2080683187668252</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3719491872685845</v>
+        <v>0.3675212207534823</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8429,22 +8429,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2447111985370244</v>
+        <v>0.2466111985370244</v>
       </c>
       <c r="C86">
-        <v>-43.90726158655211</v>
+        <v>-45.10644314165231</v>
       </c>
       <c r="D86">
-        <v>31.20833841344789</v>
+        <v>30.91305685834769</v>
       </c>
       <c r="E86">
-        <v>74.63759999999999</v>
+        <v>75.5415</v>
       </c>
       <c r="F86">
-        <v>75.9276</v>
+        <v>76.83150000000001</v>
       </c>
       <c r="G86">
         <v>0.8120000000000001</v>
@@ -8465,37 +8465,37 @@
         <v>6.58</v>
       </c>
       <c r="M86">
-        <v>17.90372808</v>
+        <v>18.1168677</v>
       </c>
       <c r="N86">
-        <v>-11.32372808</v>
+        <v>-11.5368677</v>
       </c>
       <c r="O86">
-        <v>-3.6235929856</v>
+        <v>-3.691797664000001</v>
       </c>
       <c r="P86">
-        <v>-7.7001350944</v>
+        <v>-7.845070036000003</v>
       </c>
       <c r="Q86">
-        <v>-14.2801350944</v>
+        <v>-14.425070036</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.43708631733057</v>
+        <v>0.4631720718192747</v>
       </c>
       <c r="T86">
-        <v>5.099772424510971</v>
+        <v>5.439757252811702</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.1176067906411143</v>
+        <v>0.1162231813394542</v>
       </c>
       <c r="W86">
-        <v>0.2080683187668252</v>
+        <v>0.2083945738401567</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3675212207534823</v>
+        <v>0.3631974416857943</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8511,22 +8511,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2466111985370244</v>
+        <v>0.2485111985370244</v>
       </c>
       <c r="C87">
-        <v>-45.10644314165231</v>
+        <v>-46.30008938386663</v>
       </c>
       <c r="D87">
-        <v>30.91305685834769</v>
+        <v>30.62331061613337</v>
       </c>
       <c r="E87">
-        <v>75.5415</v>
+        <v>76.44539999999999</v>
       </c>
       <c r="F87">
-        <v>76.83150000000001</v>
+        <v>77.7354</v>
       </c>
       <c r="G87">
         <v>0.8120000000000001</v>
@@ -8547,37 +8547,37 @@
         <v>6.58</v>
       </c>
       <c r="M87">
-        <v>18.1168677</v>
+        <v>18.33000732</v>
       </c>
       <c r="N87">
-        <v>-11.5368677</v>
+        <v>-11.75000732</v>
       </c>
       <c r="O87">
-        <v>-3.691797664000001</v>
+        <v>-3.7600023424</v>
       </c>
       <c r="P87">
-        <v>-7.845070036000003</v>
+        <v>-7.9900049776</v>
       </c>
       <c r="Q87">
-        <v>-14.425070036</v>
+        <v>-14.5700049776</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4631720718192747</v>
+        <v>0.4929843626635086</v>
       </c>
       <c r="T87">
-        <v>5.439757252811702</v>
+        <v>5.828311342298253</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.1162231813394542</v>
+        <v>0.1148717489982977</v>
       </c>
       <c r="W87">
-        <v>0.2083945738401567</v>
+        <v>0.2087132415862014</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3631974416857943</v>
+        <v>0.3589742156196803</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8593,22 +8593,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2485111985370244</v>
+        <v>0.2504111985370244</v>
       </c>
       <c r="C88">
-        <v>-46.30008938386663</v>
+        <v>-47.48835451435153</v>
       </c>
       <c r="D88">
-        <v>30.62331061613337</v>
+        <v>30.33894548564848</v>
       </c>
       <c r="E88">
-        <v>76.44539999999999</v>
+        <v>77.3493</v>
       </c>
       <c r="F88">
-        <v>77.7354</v>
+        <v>78.63930000000001</v>
       </c>
       <c r="G88">
         <v>0.8120000000000001</v>
@@ -8629,37 +8629,37 @@
         <v>6.58</v>
       </c>
       <c r="M88">
-        <v>18.33000732</v>
+        <v>18.54314694</v>
       </c>
       <c r="N88">
-        <v>-11.75000732</v>
+        <v>-11.96314694</v>
       </c>
       <c r="O88">
-        <v>-3.7600023424</v>
+        <v>-3.828207020800001</v>
       </c>
       <c r="P88">
-        <v>-7.9900049776</v>
+        <v>-8.134939919200002</v>
       </c>
       <c r="Q88">
-        <v>-14.5700049776</v>
+        <v>-14.7149399192</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4929843626635086</v>
+        <v>0.5273831597914708</v>
       </c>
       <c r="T88">
-        <v>5.828311342298253</v>
+        <v>6.276642984013503</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.1148717489982977</v>
+        <v>0.1135513840672828</v>
       </c>
       <c r="W88">
-        <v>0.2087132415862014</v>
+        <v>0.2090245836369347</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3589742156196803</v>
+        <v>0.3548480752102587</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8675,22 +8675,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2504111985370244</v>
+        <v>0.2523111985370244</v>
       </c>
       <c r="C89">
-        <v>-47.48835451435153</v>
+        <v>-48.67138705937134</v>
       </c>
       <c r="D89">
-        <v>30.33894548564848</v>
+        <v>30.05981294062866</v>
       </c>
       <c r="E89">
-        <v>77.3493</v>
+        <v>78.25319999999999</v>
       </c>
       <c r="F89">
-        <v>78.63930000000001</v>
+        <v>79.5432</v>
       </c>
       <c r="G89">
         <v>0.8120000000000001</v>
@@ -8711,37 +8711,37 @@
         <v>6.58</v>
       </c>
       <c r="M89">
-        <v>18.54314694</v>
+        <v>18.75628656</v>
       </c>
       <c r="N89">
-        <v>-11.96314694</v>
+        <v>-12.17628656</v>
       </c>
       <c r="O89">
-        <v>-3.828207020800001</v>
+        <v>-3.8964116992</v>
       </c>
       <c r="P89">
-        <v>-8.134939919200002</v>
+        <v>-8.2798748608</v>
       </c>
       <c r="Q89">
-        <v>-14.7149399192</v>
+        <v>-14.8598748608</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5273831597914708</v>
+        <v>0.5675150897740934</v>
       </c>
       <c r="T89">
-        <v>6.276642984013503</v>
+        <v>6.799696566014629</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.1135513840672828</v>
+        <v>0.1122610274301546</v>
       </c>
       <c r="W89">
-        <v>0.2090245836369347</v>
+        <v>0.2093288497319696</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3548480752102587</v>
+        <v>0.3508157107192331</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8757,22 +8757,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2523111985370244</v>
+        <v>0.2542111985370244</v>
       </c>
       <c r="C90">
-        <v>-48.67138705937134</v>
+        <v>-49.84933012897659</v>
       </c>
       <c r="D90">
-        <v>30.05981294062866</v>
+        <v>29.78576987102342</v>
       </c>
       <c r="E90">
-        <v>78.25319999999999</v>
+        <v>79.1571</v>
       </c>
       <c r="F90">
-        <v>79.5432</v>
+        <v>80.44710000000001</v>
       </c>
       <c r="G90">
         <v>0.8120000000000001</v>
@@ -8793,37 +8793,37 @@
         <v>6.58</v>
       </c>
       <c r="M90">
-        <v>18.75628656</v>
+        <v>18.96942618</v>
       </c>
       <c r="N90">
-        <v>-12.17628656</v>
+        <v>-12.38942618</v>
       </c>
       <c r="O90">
-        <v>-3.8964116992</v>
+        <v>-3.964616377600001</v>
       </c>
       <c r="P90">
-        <v>-8.2798748608</v>
+        <v>-8.424809802400002</v>
       </c>
       <c r="Q90">
-        <v>-14.8598748608</v>
+        <v>-15.0048098024</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5675150897740934</v>
+        <v>0.6149437342990109</v>
       </c>
       <c r="T90">
-        <v>6.799696566014629</v>
+        <v>7.417850799288687</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.1122610274301546</v>
+        <v>0.1109996675713888</v>
       </c>
       <c r="W90">
-        <v>0.2093288497319696</v>
+        <v>0.2096262783866665</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8831,7 +8831,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3508157107192331</v>
+        <v>0.34687396116059</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8839,22 +8839,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2542111985370244</v>
+        <v>0.2561111985370244</v>
       </c>
       <c r="C91">
-        <v>-49.84933012897659</v>
+        <v>-51.02232166166061</v>
       </c>
       <c r="D91">
-        <v>29.78576987102342</v>
+        <v>29.51667833833939</v>
       </c>
       <c r="E91">
-        <v>79.1571</v>
+        <v>80.06099999999999</v>
       </c>
       <c r="F91">
-        <v>80.44710000000001</v>
+        <v>81.351</v>
       </c>
       <c r="G91">
         <v>0.8120000000000001</v>
@@ -8875,37 +8875,37 @@
         <v>6.58</v>
       </c>
       <c r="M91">
-        <v>18.96942618</v>
+        <v>19.1825658</v>
       </c>
       <c r="N91">
-        <v>-12.38942618</v>
+        <v>-12.6025658</v>
       </c>
       <c r="O91">
-        <v>-3.964616377600001</v>
+        <v>-4.032821056</v>
       </c>
       <c r="P91">
-        <v>-8.424809802400002</v>
+        <v>-8.569744743999999</v>
       </c>
       <c r="Q91">
-        <v>-15.0048098024</v>
+        <v>-15.149744744</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6149437342990109</v>
+        <v>0.6718581077289121</v>
       </c>
       <c r="T91">
-        <v>7.417850799288687</v>
+        <v>8.159635879217555</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.1109996675713888</v>
+        <v>0.1097663379317067</v>
       </c>
       <c r="W91">
-        <v>0.2096262783866665</v>
+        <v>0.2099170975157036</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8913,7 +8913,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.34687396116059</v>
+        <v>0.3430198060365836</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8921,22 +8921,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2561111985370244</v>
+        <v>0.2580111985370244</v>
       </c>
       <c r="C92">
-        <v>-51.02232166166061</v>
+        <v>-52.19049465587332</v>
       </c>
       <c r="D92">
-        <v>29.51667833833939</v>
+        <v>29.25240534412669</v>
       </c>
       <c r="E92">
-        <v>80.06099999999999</v>
+        <v>80.9649</v>
       </c>
       <c r="F92">
-        <v>81.351</v>
+        <v>82.25490000000001</v>
       </c>
       <c r="G92">
         <v>0.8120000000000001</v>
@@ -8957,37 +8957,37 @@
         <v>6.58</v>
       </c>
       <c r="M92">
-        <v>19.1825658</v>
+        <v>19.39570542</v>
       </c>
       <c r="N92">
-        <v>-12.6025658</v>
+        <v>-12.81570542</v>
       </c>
       <c r="O92">
-        <v>-4.032821056</v>
+        <v>-4.101025734400001</v>
       </c>
       <c r="P92">
-        <v>-8.569744743999999</v>
+        <v>-8.7146796856</v>
       </c>
       <c r="Q92">
-        <v>-15.149744744</v>
+        <v>-15.2946796856</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6718581077289121</v>
+        <v>0.7414201196987913</v>
       </c>
       <c r="T92">
-        <v>8.159635879217555</v>
+        <v>9.066262088019508</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.1097663379317067</v>
+        <v>0.1085601144379517</v>
       </c>
       <c r="W92">
-        <v>0.2099170975157036</v>
+        <v>0.210201525015531</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3430198060365836</v>
+        <v>0.339250357618599</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9003,22 +9003,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2580111985370244</v>
+        <v>0.2599111985370244</v>
       </c>
       <c r="C93">
-        <v>-52.19049465587332</v>
+        <v>-53.35397738920816</v>
       </c>
       <c r="D93">
-        <v>29.25240534412669</v>
+        <v>28.99282261079184</v>
       </c>
       <c r="E93">
-        <v>80.9649</v>
+        <v>81.86879999999999</v>
       </c>
       <c r="F93">
-        <v>82.25490000000001</v>
+        <v>83.1588</v>
       </c>
       <c r="G93">
         <v>0.8120000000000001</v>
@@ -9039,37 +9039,37 @@
         <v>6.58</v>
       </c>
       <c r="M93">
-        <v>19.39570542</v>
+        <v>19.60884504</v>
       </c>
       <c r="N93">
-        <v>-12.81570542</v>
+        <v>-13.02884504</v>
       </c>
       <c r="O93">
-        <v>-4.101025734400001</v>
+        <v>-4.169230412800001</v>
       </c>
       <c r="P93">
-        <v>-8.7146796856</v>
+        <v>-8.859614627200001</v>
       </c>
       <c r="Q93">
-        <v>-15.2946796856</v>
+        <v>-15.4396146272</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7414201196987913</v>
+        <v>0.8283726346611404</v>
       </c>
       <c r="T93">
-        <v>9.066262088019508</v>
+        <v>10.19954484902195</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.1085601144379517</v>
+        <v>0.1073801131940609</v>
       </c>
       <c r="W93">
-        <v>0.210201525015531</v>
+        <v>0.2104797693088404</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.339250357618599</v>
+        <v>0.3355628537314403</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9085,22 +9085,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2599111985370244</v>
+        <v>0.2618111985370244</v>
       </c>
       <c r="C94">
-        <v>-53.35397738920816</v>
+        <v>-54.51289362602175</v>
       </c>
       <c r="D94">
-        <v>28.99282261079184</v>
+        <v>28.73780637397826</v>
       </c>
       <c r="E94">
-        <v>81.86879999999999</v>
+        <v>82.7727</v>
       </c>
       <c r="F94">
-        <v>83.1588</v>
+        <v>84.06270000000001</v>
       </c>
       <c r="G94">
         <v>0.8120000000000001</v>
@@ -9121,37 +9121,37 @@
         <v>6.58</v>
       </c>
       <c r="M94">
-        <v>19.60884504</v>
+        <v>19.82198466</v>
       </c>
       <c r="N94">
-        <v>-13.02884504</v>
+        <v>-13.24198466</v>
       </c>
       <c r="O94">
-        <v>-4.169230412800001</v>
+        <v>-4.237435091200001</v>
       </c>
       <c r="P94">
-        <v>-8.859614627200001</v>
+        <v>-9.004549568800002</v>
       </c>
       <c r="Q94">
-        <v>-15.4396146272</v>
+        <v>-15.5845495688</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8283726346611404</v>
+        <v>0.9401687253270177</v>
       </c>
       <c r="T94">
-        <v>10.19954484902195</v>
+        <v>11.65662268459651</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.1073801131940609</v>
+        <v>0.1062254883210065</v>
       </c>
       <c r="W94">
-        <v>0.2104797693088404</v>
+        <v>0.2107520298539067</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9159,7 +9159,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3355628537314403</v>
+        <v>0.3319546510031453</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9167,22 +9167,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2618111985370244</v>
+        <v>0.2637111985370244</v>
       </c>
       <c r="C95">
-        <v>-54.51289362602175</v>
+        <v>-55.66736281419168</v>
       </c>
       <c r="D95">
-        <v>28.73780637397826</v>
+        <v>28.48723718580833</v>
       </c>
       <c r="E95">
-        <v>82.7727</v>
+        <v>83.67659999999999</v>
       </c>
       <c r="F95">
-        <v>84.06270000000001</v>
+        <v>84.9666</v>
       </c>
       <c r="G95">
         <v>0.8120000000000001</v>
@@ -9203,37 +9203,37 @@
         <v>6.58</v>
       </c>
       <c r="M95">
-        <v>19.82198466</v>
+        <v>20.03512428</v>
       </c>
       <c r="N95">
-        <v>-13.24198466</v>
+        <v>-13.45512428</v>
       </c>
       <c r="O95">
-        <v>-4.237435091200001</v>
+        <v>-4.305639769600001</v>
       </c>
       <c r="P95">
-        <v>-9.004549568800002</v>
+        <v>-9.149484510400001</v>
       </c>
       <c r="Q95">
-        <v>-15.5845495688</v>
+        <v>-15.7294845104</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9401687253270177</v>
+        <v>1.089230179548188</v>
       </c>
       <c r="T95">
-        <v>11.65662268459651</v>
+        <v>13.59939313202927</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.1062254883210065</v>
+        <v>0.1050954299346128</v>
       </c>
       <c r="W95">
-        <v>0.2107520298539067</v>
+        <v>0.2110184976214183</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3319546510031453</v>
+        <v>0.328423218545665</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9249,22 +9249,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2637111985370244</v>
+        <v>0.2656111985370244</v>
       </c>
       <c r="C96">
-        <v>-55.66736281419168</v>
+        <v>-56.81750027167008</v>
       </c>
       <c r="D96">
-        <v>28.48723718580833</v>
+        <v>28.24099972832992</v>
       </c>
       <c r="E96">
-        <v>83.67659999999999</v>
+        <v>84.5805</v>
       </c>
       <c r="F96">
-        <v>84.9666</v>
+        <v>85.87050000000001</v>
       </c>
       <c r="G96">
         <v>0.8120000000000001</v>
@@ -9285,37 +9285,37 @@
         <v>6.58</v>
       </c>
       <c r="M96">
-        <v>20.03512428</v>
+        <v>20.2482639</v>
       </c>
       <c r="N96">
-        <v>-13.45512428</v>
+        <v>-13.6682639</v>
       </c>
       <c r="O96">
-        <v>-4.305639769600001</v>
+        <v>-4.373844448000001</v>
       </c>
       <c r="P96">
-        <v>-9.149484510400001</v>
+        <v>-9.294419452</v>
       </c>
       <c r="Q96">
-        <v>-15.7294845104</v>
+        <v>-15.874419452</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.089230179548188</v>
+        <v>1.297916215457826</v>
       </c>
       <c r="T96">
-        <v>13.59939313202927</v>
+        <v>16.31927175843514</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.1050954299346128</v>
+        <v>0.1039891622510906</v>
       </c>
       <c r="W96">
-        <v>0.2110184976214183</v>
+        <v>0.2112793555411928</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.328423218545665</v>
+        <v>0.3249661320346581</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9331,22 +9331,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2656111985370244</v>
+        <v>0.2675111985370244</v>
       </c>
       <c r="C97">
-        <v>-56.81750027167008</v>
+        <v>-57.96341736344485</v>
       </c>
       <c r="D97">
-        <v>28.24099972832992</v>
+        <v>27.99898263655516</v>
       </c>
       <c r="E97">
-        <v>84.5805</v>
+        <v>85.48440000000001</v>
       </c>
       <c r="F97">
-        <v>85.87050000000001</v>
+        <v>86.77440000000001</v>
       </c>
       <c r="G97">
         <v>0.8120000000000001</v>
@@ -9367,37 +9367,37 @@
         <v>6.58</v>
       </c>
       <c r="M97">
-        <v>20.2482639</v>
+        <v>20.46140352</v>
       </c>
       <c r="N97">
-        <v>-13.6682639</v>
+        <v>-13.88140352</v>
       </c>
       <c r="O97">
-        <v>-4.373844448000001</v>
+        <v>-4.442049126400001</v>
       </c>
       <c r="P97">
-        <v>-9.294419452</v>
+        <v>-9.439354393600002</v>
       </c>
       <c r="Q97">
-        <v>-15.874419452</v>
+        <v>-16.0193543936</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.297916215457826</v>
+        <v>1.610945269322283</v>
       </c>
       <c r="T97">
-        <v>16.31927175843514</v>
+        <v>20.39908969804393</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.1039891622510906</v>
+        <v>0.102905941810975</v>
       </c>
       <c r="W97">
-        <v>0.2112793555411928</v>
+        <v>0.2115347789209721</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9405,7 +9405,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3249661320346581</v>
+        <v>0.321581068159297</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9413,22 +9413,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2675111985370244</v>
+        <v>0.2694111985370244</v>
       </c>
       <c r="C98">
-        <v>-57.96341736344484</v>
+        <v>-59.10522166947915</v>
       </c>
       <c r="D98">
-        <v>27.99898263655516</v>
+        <v>27.76107833052084</v>
       </c>
       <c r="E98">
-        <v>85.48439999999999</v>
+        <v>86.38829999999999</v>
       </c>
       <c r="F98">
-        <v>86.7744</v>
+        <v>87.67829999999999</v>
       </c>
       <c r="G98">
         <v>0.8120000000000001</v>
@@ -9449,37 +9449,37 @@
         <v>6.58</v>
       </c>
       <c r="M98">
-        <v>20.46140352</v>
+        <v>20.67454314</v>
       </c>
       <c r="N98">
-        <v>-13.88140352</v>
+        <v>-14.09454314</v>
       </c>
       <c r="O98">
-        <v>-4.442049126400001</v>
+        <v>-4.5102538048</v>
       </c>
       <c r="P98">
-        <v>-9.4393543936</v>
+        <v>-9.584289335200001</v>
       </c>
       <c r="Q98">
-        <v>-16.0193543936</v>
+        <v>-16.1642893352</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.610945269322279</v>
+        <v>2.132660359096372</v>
       </c>
       <c r="T98">
-        <v>20.39908969804387</v>
+        <v>27.19878626405849</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.102905941810975</v>
+        <v>0.1018450558129238</v>
       </c>
       <c r="W98">
-        <v>0.2115347789209721</v>
+        <v>0.2117849358393126</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.321581068159297</v>
+        <v>0.3182657994153867</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9495,22 +9495,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2694111985370244</v>
+        <v>0.2713111985370245</v>
       </c>
       <c r="C99">
-        <v>-59.10522166947915</v>
+        <v>-60.24301714416146</v>
       </c>
       <c r="D99">
-        <v>27.76107833052084</v>
+        <v>27.52718285583854</v>
       </c>
       <c r="E99">
-        <v>86.38829999999999</v>
+        <v>87.29219999999999</v>
       </c>
       <c r="F99">
-        <v>87.67829999999999</v>
+        <v>88.5822</v>
       </c>
       <c r="G99">
         <v>0.8120000000000001</v>
@@ -9531,37 +9531,37 @@
         <v>6.58</v>
       </c>
       <c r="M99">
-        <v>20.67454314</v>
+        <v>20.88768276</v>
       </c>
       <c r="N99">
-        <v>-14.09454314</v>
+        <v>-14.30768276</v>
       </c>
       <c r="O99">
-        <v>-4.5102538048</v>
+        <v>-4.5784584832</v>
       </c>
       <c r="P99">
-        <v>-9.584289335200001</v>
+        <v>-9.7292242768</v>
       </c>
       <c r="Q99">
-        <v>-16.1642893352</v>
+        <v>-16.3092242768</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.132660359096372</v>
+        <v>3.176090538644557</v>
       </c>
       <c r="T99">
-        <v>27.19878626405849</v>
+        <v>40.79817939608774</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.1018450558129238</v>
+        <v>0.1008058205495266</v>
       </c>
       <c r="W99">
-        <v>0.2117849358393126</v>
+        <v>0.2120299875144216</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9569,7 +9569,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3182657994153867</v>
+        <v>0.3150181892172705</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9577,22 +9577,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2713111985370245</v>
+        <v>0.2732111985370244</v>
       </c>
       <c r="C100">
-        <v>-60.24301714416146</v>
+        <v>-61.37690426776204</v>
       </c>
       <c r="D100">
-        <v>27.52718285583854</v>
+        <v>27.29719573223795</v>
       </c>
       <c r="E100">
-        <v>87.29219999999999</v>
+        <v>88.19609999999999</v>
       </c>
       <c r="F100">
-        <v>88.5822</v>
+        <v>89.48609999999999</v>
       </c>
       <c r="G100">
         <v>0.8120000000000001</v>
@@ -9613,37 +9613,37 @@
         <v>6.58</v>
       </c>
       <c r="M100">
-        <v>20.88768276</v>
+        <v>21.10082238</v>
       </c>
       <c r="N100">
-        <v>-14.30768276</v>
+        <v>-14.52082238</v>
       </c>
       <c r="O100">
-        <v>-4.5784584832</v>
+        <v>-4.6466631616</v>
       </c>
       <c r="P100">
-        <v>-9.7292242768</v>
+        <v>-9.874159218399999</v>
       </c>
       <c r="Q100">
-        <v>-16.3092242768</v>
+        <v>-16.4541592184</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.176090538644557</v>
+        <v>6.306381077289115</v>
       </c>
       <c r="T100">
-        <v>40.79817939608774</v>
+        <v>81.59635879217548</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.1008058205495266</v>
+        <v>0.09978757993791521</v>
       </c>
       <c r="W100">
-        <v>0.2120299875144216</v>
+        <v>0.2122700886506396</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9651,91 +9651,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3150181892172705</v>
+        <v>0.3118361873059849</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2732111985370244</v>
-      </c>
-      <c r="C101">
-        <v>-61.37690426776204</v>
-      </c>
-      <c r="D101">
-        <v>27.29719573223795</v>
-      </c>
-      <c r="E101">
-        <v>88.19609999999999</v>
-      </c>
-      <c r="F101">
-        <v>89.48609999999999</v>
-      </c>
-      <c r="G101">
-        <v>0.8120000000000001</v>
-      </c>
-      <c r="H101">
-        <v>89.09999999999999</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0</v>
-      </c>
-      <c r="K101">
-        <v>-6.58</v>
-      </c>
-      <c r="L101">
-        <v>6.58</v>
-      </c>
-      <c r="M101">
-        <v>21.10082238</v>
-      </c>
-      <c r="N101">
-        <v>-14.52082238</v>
-      </c>
-      <c r="O101">
-        <v>-4.6466631616</v>
-      </c>
-      <c r="P101">
-        <v>-9.874159218399999</v>
-      </c>
-      <c r="Q101">
-        <v>-16.4541592184</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.306381077289115</v>
-      </c>
-      <c r="T101">
-        <v>81.59635879217548</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.09978757993791521</v>
-      </c>
-      <c r="W101">
-        <v>0.2122700886506396</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3118361873059849</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
